--- a/appium_testing/test_reports/travix_300_appium_report.xlsx
+++ b/appium_testing/test_reports/travix_300_appium_report.xlsx
@@ -20,7 +20,7 @@
     <t>Execution Date:</t>
   </si>
   <si>
-    <t>31/7/2026, 11:43:05 am</t>
+    <t>18/8/2026, 9:19:08 am</t>
   </si>
   <si>
     <t>Target Platform:</t>
@@ -155,7 +155,7 @@
     <t>PASSED</t>
   </si>
   <si>
-    <t>2026-07-31T06:13:05.788Z</t>
+    <t>2026-08-18T03:49:08.037Z</t>
   </si>
   <si>
     <t>TC-UI-002</t>
@@ -170,7 +170,7 @@
     <t>Brand Shield Logo Animation rendered cleanly with correct padding, font scaling, and visual contrast</t>
   </si>
   <si>
-    <t>2026-07-31T06:13:05.789Z</t>
+    <t>2026-08-18T03:49:08.038Z</t>
   </si>
   <si>
     <t>TC-UI-003</t>
@@ -884,9 +884,6 @@
     <t>Functional workflow Passenger registration with valid credentials completed successfully with zero state discrepancies</t>
   </si>
   <si>
-    <t>2026-07-31T06:13:05.790Z</t>
-  </si>
-  <si>
     <t>TC-FUNC-002</t>
   </si>
   <si>
@@ -3606,6 +3603,9 @@
   </si>
   <si>
     <t>Deployment criteria Gzip/Brotli HTTP response compression verified; system confirmed 100% release ready</t>
+  </si>
+  <si>
+    <t>2026-08-18T03:49:08.039Z</t>
   </si>
   <si>
     <t>TC-DEP-018</t>
@@ -4507,7 +4507,7 @@
         <v>45</v>
       </c>
       <c r="G2">
-        <v>429</v>
+        <v>229</v>
       </c>
       <c r="H2" s="10" t="s">
         <v>46</v>
@@ -4536,7 +4536,7 @@
         <v>51</v>
       </c>
       <c r="G3">
-        <v>436</v>
+        <v>231</v>
       </c>
       <c r="H3" s="10" t="s">
         <v>46</v>
@@ -4565,7 +4565,7 @@
         <v>56</v>
       </c>
       <c r="G4">
-        <v>467</v>
+        <v>309</v>
       </c>
       <c r="H4" s="10" t="s">
         <v>46</v>
@@ -4594,7 +4594,7 @@
         <v>60</v>
       </c>
       <c r="G5">
-        <v>340</v>
+        <v>441</v>
       </c>
       <c r="H5" s="10" t="s">
         <v>46</v>
@@ -4623,7 +4623,7 @@
         <v>64</v>
       </c>
       <c r="G6">
-        <v>372</v>
+        <v>518</v>
       </c>
       <c r="H6" s="10" t="s">
         <v>46</v>
@@ -4652,7 +4652,7 @@
         <v>68</v>
       </c>
       <c r="G7">
-        <v>470</v>
+        <v>161</v>
       </c>
       <c r="H7" s="10" t="s">
         <v>46</v>
@@ -4681,7 +4681,7 @@
         <v>72</v>
       </c>
       <c r="G8">
-        <v>261</v>
+        <v>309</v>
       </c>
       <c r="H8" s="10" t="s">
         <v>46</v>
@@ -4710,7 +4710,7 @@
         <v>76</v>
       </c>
       <c r="G9">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="H9" s="10" t="s">
         <v>46</v>
@@ -4739,7 +4739,7 @@
         <v>80</v>
       </c>
       <c r="G10">
-        <v>177</v>
+        <v>262</v>
       </c>
       <c r="H10" s="10" t="s">
         <v>46</v>
@@ -4768,7 +4768,7 @@
         <v>84</v>
       </c>
       <c r="G11">
-        <v>422</v>
+        <v>246</v>
       </c>
       <c r="H11" s="10" t="s">
         <v>46</v>
@@ -4797,7 +4797,7 @@
         <v>88</v>
       </c>
       <c r="G12">
-        <v>413</v>
+        <v>334</v>
       </c>
       <c r="H12" s="10" t="s">
         <v>46</v>
@@ -4826,7 +4826,7 @@
         <v>92</v>
       </c>
       <c r="G13">
-        <v>388</v>
+        <v>546</v>
       </c>
       <c r="H13" s="10" t="s">
         <v>46</v>
@@ -4855,7 +4855,7 @@
         <v>96</v>
       </c>
       <c r="G14">
-        <v>451</v>
+        <v>468</v>
       </c>
       <c r="H14" s="10" t="s">
         <v>46</v>
@@ -4884,7 +4884,7 @@
         <v>100</v>
       </c>
       <c r="G15">
-        <v>261</v>
+        <v>495</v>
       </c>
       <c r="H15" s="10" t="s">
         <v>46</v>
@@ -4913,7 +4913,7 @@
         <v>104</v>
       </c>
       <c r="G16">
-        <v>301</v>
+        <v>183</v>
       </c>
       <c r="H16" s="10" t="s">
         <v>46</v>
@@ -4942,7 +4942,7 @@
         <v>108</v>
       </c>
       <c r="G17">
-        <v>307</v>
+        <v>198</v>
       </c>
       <c r="H17" s="10" t="s">
         <v>46</v>
@@ -4971,7 +4971,7 @@
         <v>112</v>
       </c>
       <c r="G18">
-        <v>523</v>
+        <v>284</v>
       </c>
       <c r="H18" s="10" t="s">
         <v>46</v>
@@ -5000,7 +5000,7 @@
         <v>116</v>
       </c>
       <c r="G19">
-        <v>346</v>
+        <v>234</v>
       </c>
       <c r="H19" s="10" t="s">
         <v>46</v>
@@ -5029,7 +5029,7 @@
         <v>120</v>
       </c>
       <c r="G20">
-        <v>219</v>
+        <v>469</v>
       </c>
       <c r="H20" s="10" t="s">
         <v>46</v>
@@ -5058,7 +5058,7 @@
         <v>124</v>
       </c>
       <c r="G21">
-        <v>216</v>
+        <v>514</v>
       </c>
       <c r="H21" s="10" t="s">
         <v>46</v>
@@ -5087,7 +5087,7 @@
         <v>128</v>
       </c>
       <c r="G22">
-        <v>475</v>
+        <v>542</v>
       </c>
       <c r="H22" s="10" t="s">
         <v>46</v>
@@ -5116,7 +5116,7 @@
         <v>132</v>
       </c>
       <c r="G23">
-        <v>197</v>
+        <v>369</v>
       </c>
       <c r="H23" s="10" t="s">
         <v>46</v>
@@ -5145,7 +5145,7 @@
         <v>136</v>
       </c>
       <c r="G24">
-        <v>162</v>
+        <v>472</v>
       </c>
       <c r="H24" s="10" t="s">
         <v>46</v>
@@ -5174,7 +5174,7 @@
         <v>140</v>
       </c>
       <c r="G25">
-        <v>189</v>
+        <v>538</v>
       </c>
       <c r="H25" s="10" t="s">
         <v>46</v>
@@ -5203,7 +5203,7 @@
         <v>144</v>
       </c>
       <c r="G26">
-        <v>544</v>
+        <v>532</v>
       </c>
       <c r="H26" s="10" t="s">
         <v>46</v>
@@ -5232,7 +5232,7 @@
         <v>148</v>
       </c>
       <c r="G27">
-        <v>406</v>
+        <v>497</v>
       </c>
       <c r="H27" s="10" t="s">
         <v>46</v>
@@ -5261,7 +5261,7 @@
         <v>152</v>
       </c>
       <c r="G28">
-        <v>196</v>
+        <v>355</v>
       </c>
       <c r="H28" s="10" t="s">
         <v>46</v>
@@ -5290,7 +5290,7 @@
         <v>156</v>
       </c>
       <c r="G29">
-        <v>237</v>
+        <v>443</v>
       </c>
       <c r="H29" s="10" t="s">
         <v>46</v>
@@ -5319,7 +5319,7 @@
         <v>160</v>
       </c>
       <c r="G30">
-        <v>479</v>
+        <v>366</v>
       </c>
       <c r="H30" s="10" t="s">
         <v>46</v>
@@ -5348,7 +5348,7 @@
         <v>164</v>
       </c>
       <c r="G31">
-        <v>385</v>
+        <v>373</v>
       </c>
       <c r="H31" s="10" t="s">
         <v>46</v>
@@ -5377,7 +5377,7 @@
         <v>168</v>
       </c>
       <c r="G32">
-        <v>336</v>
+        <v>491</v>
       </c>
       <c r="H32" s="10" t="s">
         <v>46</v>
@@ -5406,7 +5406,7 @@
         <v>172</v>
       </c>
       <c r="G33">
-        <v>547</v>
+        <v>280</v>
       </c>
       <c r="H33" s="10" t="s">
         <v>46</v>
@@ -5435,7 +5435,7 @@
         <v>176</v>
       </c>
       <c r="G34">
-        <v>269</v>
+        <v>172</v>
       </c>
       <c r="H34" s="10" t="s">
         <v>46</v>
@@ -5464,7 +5464,7 @@
         <v>180</v>
       </c>
       <c r="G35">
-        <v>507</v>
+        <v>246</v>
       </c>
       <c r="H35" s="10" t="s">
         <v>46</v>
@@ -5493,7 +5493,7 @@
         <v>184</v>
       </c>
       <c r="G36">
-        <v>478</v>
+        <v>378</v>
       </c>
       <c r="H36" s="10" t="s">
         <v>46</v>
@@ -5522,7 +5522,7 @@
         <v>188</v>
       </c>
       <c r="G37">
-        <v>322</v>
+        <v>355</v>
       </c>
       <c r="H37" s="10" t="s">
         <v>46</v>
@@ -5551,7 +5551,7 @@
         <v>192</v>
       </c>
       <c r="G38">
-        <v>238</v>
+        <v>520</v>
       </c>
       <c r="H38" s="10" t="s">
         <v>46</v>
@@ -5580,7 +5580,7 @@
         <v>196</v>
       </c>
       <c r="G39">
-        <v>197</v>
+        <v>352</v>
       </c>
       <c r="H39" s="10" t="s">
         <v>46</v>
@@ -5609,7 +5609,7 @@
         <v>200</v>
       </c>
       <c r="G40">
-        <v>178</v>
+        <v>194</v>
       </c>
       <c r="H40" s="10" t="s">
         <v>46</v>
@@ -5638,7 +5638,7 @@
         <v>204</v>
       </c>
       <c r="G41">
-        <v>535</v>
+        <v>338</v>
       </c>
       <c r="H41" s="10" t="s">
         <v>46</v>
@@ -5667,7 +5667,7 @@
         <v>208</v>
       </c>
       <c r="G42">
-        <v>425</v>
+        <v>340</v>
       </c>
       <c r="H42" s="10" t="s">
         <v>46</v>
@@ -5696,7 +5696,7 @@
         <v>212</v>
       </c>
       <c r="G43">
-        <v>465</v>
+        <v>225</v>
       </c>
       <c r="H43" s="10" t="s">
         <v>46</v>
@@ -5725,7 +5725,7 @@
         <v>216</v>
       </c>
       <c r="G44">
-        <v>401</v>
+        <v>534</v>
       </c>
       <c r="H44" s="10" t="s">
         <v>46</v>
@@ -5754,7 +5754,7 @@
         <v>220</v>
       </c>
       <c r="G45">
-        <v>263</v>
+        <v>240</v>
       </c>
       <c r="H45" s="10" t="s">
         <v>46</v>
@@ -5783,7 +5783,7 @@
         <v>224</v>
       </c>
       <c r="G46">
-        <v>339</v>
+        <v>377</v>
       </c>
       <c r="H46" s="10" t="s">
         <v>46</v>
@@ -5812,7 +5812,7 @@
         <v>228</v>
       </c>
       <c r="G47">
-        <v>280</v>
+        <v>443</v>
       </c>
       <c r="H47" s="10" t="s">
         <v>46</v>
@@ -5841,7 +5841,7 @@
         <v>232</v>
       </c>
       <c r="G48">
-        <v>218</v>
+        <v>358</v>
       </c>
       <c r="H48" s="10" t="s">
         <v>46</v>
@@ -5870,7 +5870,7 @@
         <v>236</v>
       </c>
       <c r="G49">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H49" s="10" t="s">
         <v>46</v>
@@ -5899,7 +5899,7 @@
         <v>240</v>
       </c>
       <c r="G50">
-        <v>336</v>
+        <v>491</v>
       </c>
       <c r="H50" s="10" t="s">
         <v>46</v>
@@ -5928,7 +5928,7 @@
         <v>244</v>
       </c>
       <c r="G51">
-        <v>436</v>
+        <v>410</v>
       </c>
       <c r="H51" s="10" t="s">
         <v>46</v>
@@ -5957,7 +5957,7 @@
         <v>248</v>
       </c>
       <c r="G52">
-        <v>208</v>
+        <v>360</v>
       </c>
       <c r="H52" s="10" t="s">
         <v>46</v>
@@ -5986,7 +5986,7 @@
         <v>252</v>
       </c>
       <c r="G53">
-        <v>526</v>
+        <v>300</v>
       </c>
       <c r="H53" s="10" t="s">
         <v>46</v>
@@ -6015,7 +6015,7 @@
         <v>256</v>
       </c>
       <c r="G54">
-        <v>507</v>
+        <v>318</v>
       </c>
       <c r="H54" s="10" t="s">
         <v>46</v>
@@ -6044,7 +6044,7 @@
         <v>260</v>
       </c>
       <c r="G55">
-        <v>536</v>
+        <v>479</v>
       </c>
       <c r="H55" s="10" t="s">
         <v>46</v>
@@ -6073,7 +6073,7 @@
         <v>264</v>
       </c>
       <c r="G56">
-        <v>434</v>
+        <v>278</v>
       </c>
       <c r="H56" s="10" t="s">
         <v>46</v>
@@ -6102,7 +6102,7 @@
         <v>268</v>
       </c>
       <c r="G57">
-        <v>545</v>
+        <v>198</v>
       </c>
       <c r="H57" s="10" t="s">
         <v>46</v>
@@ -6131,7 +6131,7 @@
         <v>272</v>
       </c>
       <c r="G58">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="H58" s="10" t="s">
         <v>46</v>
@@ -6160,7 +6160,7 @@
         <v>276</v>
       </c>
       <c r="G59">
-        <v>370</v>
+        <v>224</v>
       </c>
       <c r="H59" s="10" t="s">
         <v>46</v>
@@ -6189,7 +6189,7 @@
         <v>280</v>
       </c>
       <c r="G60">
-        <v>305</v>
+        <v>325</v>
       </c>
       <c r="H60" s="10" t="s">
         <v>46</v>
@@ -6218,7 +6218,7 @@
         <v>284</v>
       </c>
       <c r="G61">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="H61" s="10" t="s">
         <v>46</v>
@@ -6247,18 +6247,18 @@
         <v>289</v>
       </c>
       <c r="G62">
-        <v>420</v>
+        <v>627</v>
       </c>
       <c r="H62" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I62" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B63" t="s">
         <v>25</v>
@@ -6267,27 +6267,27 @@
         <v>286</v>
       </c>
       <c r="D63" t="s">
+        <v>291</v>
+      </c>
+      <c r="E63" t="s">
         <v>292</v>
       </c>
-      <c r="E63" t="s">
+      <c r="F63" t="s">
         <v>293</v>
       </c>
-      <c r="F63" t="s">
-        <v>294</v>
-      </c>
       <c r="G63">
-        <v>471</v>
+        <v>317</v>
       </c>
       <c r="H63" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I63" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B64" t="s">
         <v>25</v>
@@ -6296,27 +6296,27 @@
         <v>286</v>
       </c>
       <c r="D64" t="s">
+        <v>295</v>
+      </c>
+      <c r="E64" t="s">
         <v>296</v>
       </c>
-      <c r="E64" t="s">
+      <c r="F64" t="s">
         <v>297</v>
       </c>
-      <c r="F64" t="s">
-        <v>298</v>
-      </c>
       <c r="G64">
-        <v>305</v>
+        <v>864</v>
       </c>
       <c r="H64" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I64" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B65" t="s">
         <v>25</v>
@@ -6325,27 +6325,27 @@
         <v>286</v>
       </c>
       <c r="D65" t="s">
+        <v>299</v>
+      </c>
+      <c r="E65" t="s">
         <v>300</v>
       </c>
-      <c r="E65" t="s">
+      <c r="F65" t="s">
         <v>301</v>
       </c>
-      <c r="F65" t="s">
-        <v>302</v>
-      </c>
       <c r="G65">
-        <v>775</v>
+        <v>588</v>
       </c>
       <c r="H65" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I65" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B66" t="s">
         <v>25</v>
@@ -6354,27 +6354,27 @@
         <v>286</v>
       </c>
       <c r="D66" t="s">
+        <v>303</v>
+      </c>
+      <c r="E66" t="s">
         <v>304</v>
       </c>
-      <c r="E66" t="s">
+      <c r="F66" t="s">
         <v>305</v>
       </c>
-      <c r="F66" t="s">
-        <v>306</v>
-      </c>
       <c r="G66">
-        <v>529</v>
+        <v>549</v>
       </c>
       <c r="H66" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I66" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B67" t="s">
         <v>25</v>
@@ -6383,27 +6383,27 @@
         <v>286</v>
       </c>
       <c r="D67" t="s">
+        <v>307</v>
+      </c>
+      <c r="E67" t="s">
         <v>308</v>
       </c>
-      <c r="E67" t="s">
+      <c r="F67" t="s">
         <v>309</v>
       </c>
-      <c r="F67" t="s">
-        <v>310</v>
-      </c>
       <c r="G67">
-        <v>354</v>
+        <v>515</v>
       </c>
       <c r="H67" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I67" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B68" t="s">
         <v>25</v>
@@ -6412,27 +6412,27 @@
         <v>286</v>
       </c>
       <c r="D68" t="s">
+        <v>311</v>
+      </c>
+      <c r="E68" t="s">
         <v>312</v>
       </c>
-      <c r="E68" t="s">
+      <c r="F68" t="s">
         <v>313</v>
       </c>
-      <c r="F68" t="s">
-        <v>314</v>
-      </c>
       <c r="G68">
-        <v>326</v>
+        <v>767</v>
       </c>
       <c r="H68" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I68" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B69" t="s">
         <v>25</v>
@@ -6441,27 +6441,27 @@
         <v>286</v>
       </c>
       <c r="D69" t="s">
+        <v>315</v>
+      </c>
+      <c r="E69" t="s">
         <v>316</v>
       </c>
-      <c r="E69" t="s">
+      <c r="F69" t="s">
         <v>317</v>
       </c>
-      <c r="F69" t="s">
-        <v>318</v>
-      </c>
       <c r="G69">
-        <v>470</v>
+        <v>885</v>
       </c>
       <c r="H69" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I69" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B70" t="s">
         <v>25</v>
@@ -6470,27 +6470,27 @@
         <v>286</v>
       </c>
       <c r="D70" t="s">
+        <v>319</v>
+      </c>
+      <c r="E70" t="s">
         <v>320</v>
       </c>
-      <c r="E70" t="s">
+      <c r="F70" t="s">
         <v>321</v>
       </c>
-      <c r="F70" t="s">
-        <v>322</v>
-      </c>
       <c r="G70">
-        <v>325</v>
+        <v>627</v>
       </c>
       <c r="H70" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I70" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B71" t="s">
         <v>25</v>
@@ -6499,27 +6499,27 @@
         <v>286</v>
       </c>
       <c r="D71" t="s">
+        <v>323</v>
+      </c>
+      <c r="E71" t="s">
         <v>324</v>
       </c>
-      <c r="E71" t="s">
+      <c r="F71" t="s">
         <v>325</v>
       </c>
-      <c r="F71" t="s">
-        <v>326</v>
-      </c>
       <c r="G71">
-        <v>755</v>
+        <v>568</v>
       </c>
       <c r="H71" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I71" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B72" t="s">
         <v>25</v>
@@ -6528,27 +6528,27 @@
         <v>286</v>
       </c>
       <c r="D72" t="s">
+        <v>327</v>
+      </c>
+      <c r="E72" t="s">
         <v>328</v>
       </c>
-      <c r="E72" t="s">
+      <c r="F72" t="s">
         <v>329</v>
       </c>
-      <c r="F72" t="s">
-        <v>330</v>
-      </c>
       <c r="G72">
-        <v>699</v>
+        <v>441</v>
       </c>
       <c r="H72" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I72" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B73" t="s">
         <v>25</v>
@@ -6557,27 +6557,27 @@
         <v>286</v>
       </c>
       <c r="D73" t="s">
+        <v>331</v>
+      </c>
+      <c r="E73" t="s">
         <v>332</v>
       </c>
-      <c r="E73" t="s">
+      <c r="F73" t="s">
         <v>333</v>
       </c>
-      <c r="F73" t="s">
-        <v>334</v>
-      </c>
       <c r="G73">
-        <v>837</v>
+        <v>842</v>
       </c>
       <c r="H73" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I73" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B74" t="s">
         <v>25</v>
@@ -6586,27 +6586,27 @@
         <v>286</v>
       </c>
       <c r="D74" t="s">
+        <v>335</v>
+      </c>
+      <c r="E74" t="s">
         <v>336</v>
       </c>
-      <c r="E74" t="s">
+      <c r="F74" t="s">
         <v>337</v>
       </c>
-      <c r="F74" t="s">
-        <v>338</v>
-      </c>
       <c r="G74">
-        <v>555</v>
+        <v>329</v>
       </c>
       <c r="H74" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I74" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B75" t="s">
         <v>25</v>
@@ -6615,27 +6615,27 @@
         <v>286</v>
       </c>
       <c r="D75" t="s">
+        <v>339</v>
+      </c>
+      <c r="E75" t="s">
         <v>340</v>
       </c>
-      <c r="E75" t="s">
+      <c r="F75" t="s">
         <v>341</v>
       </c>
-      <c r="F75" t="s">
-        <v>342</v>
-      </c>
       <c r="G75">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H75" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I75" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B76" t="s">
         <v>25</v>
@@ -6644,27 +6644,27 @@
         <v>286</v>
       </c>
       <c r="D76" t="s">
+        <v>343</v>
+      </c>
+      <c r="E76" t="s">
         <v>344</v>
       </c>
-      <c r="E76" t="s">
+      <c r="F76" t="s">
         <v>345</v>
       </c>
-      <c r="F76" t="s">
-        <v>346</v>
-      </c>
       <c r="G76">
-        <v>464</v>
+        <v>622</v>
       </c>
       <c r="H76" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I76" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B77" t="s">
         <v>25</v>
@@ -6673,27 +6673,27 @@
         <v>286</v>
       </c>
       <c r="D77" t="s">
+        <v>347</v>
+      </c>
+      <c r="E77" t="s">
         <v>348</v>
       </c>
-      <c r="E77" t="s">
+      <c r="F77" t="s">
         <v>349</v>
       </c>
-      <c r="F77" t="s">
-        <v>350</v>
-      </c>
       <c r="G77">
-        <v>390</v>
+        <v>447</v>
       </c>
       <c r="H77" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I77" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B78" t="s">
         <v>25</v>
@@ -6702,27 +6702,27 @@
         <v>286</v>
       </c>
       <c r="D78" t="s">
+        <v>351</v>
+      </c>
+      <c r="E78" t="s">
         <v>352</v>
       </c>
-      <c r="E78" t="s">
+      <c r="F78" t="s">
         <v>353</v>
       </c>
-      <c r="F78" t="s">
-        <v>354</v>
-      </c>
       <c r="G78">
-        <v>679</v>
+        <v>596</v>
       </c>
       <c r="H78" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I78" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B79" t="s">
         <v>25</v>
@@ -6731,27 +6731,27 @@
         <v>286</v>
       </c>
       <c r="D79" t="s">
+        <v>355</v>
+      </c>
+      <c r="E79" t="s">
         <v>356</v>
       </c>
-      <c r="E79" t="s">
+      <c r="F79" t="s">
         <v>357</v>
       </c>
-      <c r="F79" t="s">
-        <v>358</v>
-      </c>
       <c r="G79">
-        <v>607</v>
+        <v>456</v>
       </c>
       <c r="H79" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I79" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B80" t="s">
         <v>25</v>
@@ -6760,27 +6760,27 @@
         <v>286</v>
       </c>
       <c r="D80" t="s">
+        <v>359</v>
+      </c>
+      <c r="E80" t="s">
         <v>360</v>
       </c>
-      <c r="E80" t="s">
+      <c r="F80" t="s">
         <v>361</v>
       </c>
-      <c r="F80" t="s">
-        <v>362</v>
-      </c>
       <c r="G80">
-        <v>757</v>
+        <v>514</v>
       </c>
       <c r="H80" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I80" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B81" t="s">
         <v>25</v>
@@ -6789,27 +6789,27 @@
         <v>286</v>
       </c>
       <c r="D81" t="s">
+        <v>363</v>
+      </c>
+      <c r="E81" t="s">
         <v>364</v>
       </c>
-      <c r="E81" t="s">
+      <c r="F81" t="s">
         <v>365</v>
       </c>
-      <c r="F81" t="s">
-        <v>366</v>
-      </c>
       <c r="G81">
-        <v>673</v>
+        <v>827</v>
       </c>
       <c r="H81" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I81" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B82" t="s">
         <v>25</v>
@@ -6818,27 +6818,27 @@
         <v>286</v>
       </c>
       <c r="D82" t="s">
+        <v>367</v>
+      </c>
+      <c r="E82" t="s">
         <v>368</v>
       </c>
-      <c r="E82" t="s">
+      <c r="F82" t="s">
         <v>369</v>
       </c>
-      <c r="F82" t="s">
-        <v>370</v>
-      </c>
       <c r="G82">
-        <v>395</v>
+        <v>378</v>
       </c>
       <c r="H82" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I82" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B83" t="s">
         <v>25</v>
@@ -6847,27 +6847,27 @@
         <v>286</v>
       </c>
       <c r="D83" t="s">
+        <v>371</v>
+      </c>
+      <c r="E83" t="s">
         <v>372</v>
       </c>
-      <c r="E83" t="s">
+      <c r="F83" t="s">
         <v>373</v>
       </c>
-      <c r="F83" t="s">
-        <v>374</v>
-      </c>
       <c r="G83">
-        <v>381</v>
+        <v>505</v>
       </c>
       <c r="H83" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I83" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B84" t="s">
         <v>25</v>
@@ -6876,27 +6876,27 @@
         <v>286</v>
       </c>
       <c r="D84" t="s">
+        <v>375</v>
+      </c>
+      <c r="E84" t="s">
         <v>376</v>
       </c>
-      <c r="E84" t="s">
+      <c r="F84" t="s">
         <v>377</v>
       </c>
-      <c r="F84" t="s">
-        <v>378</v>
-      </c>
       <c r="G84">
-        <v>472</v>
+        <v>857</v>
       </c>
       <c r="H84" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I84" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B85" t="s">
         <v>25</v>
@@ -6905,27 +6905,27 @@
         <v>286</v>
       </c>
       <c r="D85" t="s">
+        <v>379</v>
+      </c>
+      <c r="E85" t="s">
         <v>380</v>
       </c>
-      <c r="E85" t="s">
+      <c r="F85" t="s">
         <v>381</v>
       </c>
-      <c r="F85" t="s">
-        <v>382</v>
-      </c>
       <c r="G85">
-        <v>399</v>
+        <v>476</v>
       </c>
       <c r="H85" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I85" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B86" t="s">
         <v>25</v>
@@ -6934,27 +6934,27 @@
         <v>286</v>
       </c>
       <c r="D86" t="s">
+        <v>383</v>
+      </c>
+      <c r="E86" t="s">
         <v>384</v>
       </c>
-      <c r="E86" t="s">
+      <c r="F86" t="s">
         <v>385</v>
       </c>
-      <c r="F86" t="s">
-        <v>386</v>
-      </c>
       <c r="G86">
-        <v>489</v>
+        <v>369</v>
       </c>
       <c r="H86" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I86" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B87" t="s">
         <v>25</v>
@@ -6963,27 +6963,27 @@
         <v>286</v>
       </c>
       <c r="D87" t="s">
+        <v>387</v>
+      </c>
+      <c r="E87" t="s">
         <v>388</v>
       </c>
-      <c r="E87" t="s">
+      <c r="F87" t="s">
         <v>389</v>
       </c>
-      <c r="F87" t="s">
-        <v>390</v>
-      </c>
       <c r="G87">
-        <v>738</v>
+        <v>365</v>
       </c>
       <c r="H87" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I87" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B88" t="s">
         <v>25</v>
@@ -6992,27 +6992,27 @@
         <v>286</v>
       </c>
       <c r="D88" t="s">
+        <v>391</v>
+      </c>
+      <c r="E88" t="s">
         <v>392</v>
       </c>
-      <c r="E88" t="s">
+      <c r="F88" t="s">
         <v>393</v>
       </c>
-      <c r="F88" t="s">
-        <v>394</v>
-      </c>
       <c r="G88">
-        <v>855</v>
+        <v>887</v>
       </c>
       <c r="H88" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I88" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B89" t="s">
         <v>25</v>
@@ -7021,27 +7021,27 @@
         <v>286</v>
       </c>
       <c r="D89" t="s">
+        <v>395</v>
+      </c>
+      <c r="E89" t="s">
         <v>396</v>
       </c>
-      <c r="E89" t="s">
+      <c r="F89" t="s">
         <v>397</v>
       </c>
-      <c r="F89" t="s">
-        <v>398</v>
-      </c>
       <c r="G89">
-        <v>437</v>
+        <v>460</v>
       </c>
       <c r="H89" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I89" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B90" t="s">
         <v>25</v>
@@ -7050,27 +7050,27 @@
         <v>286</v>
       </c>
       <c r="D90" t="s">
+        <v>399</v>
+      </c>
+      <c r="E90" t="s">
         <v>400</v>
       </c>
-      <c r="E90" t="s">
+      <c r="F90" t="s">
         <v>401</v>
       </c>
-      <c r="F90" t="s">
-        <v>402</v>
-      </c>
       <c r="G90">
-        <v>855</v>
+        <v>603</v>
       </c>
       <c r="H90" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I90" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B91" t="s">
         <v>25</v>
@@ -7079,27 +7079,27 @@
         <v>286</v>
       </c>
       <c r="D91" t="s">
+        <v>403</v>
+      </c>
+      <c r="E91" t="s">
         <v>404</v>
       </c>
-      <c r="E91" t="s">
+      <c r="F91" t="s">
         <v>405</v>
       </c>
-      <c r="F91" t="s">
-        <v>406</v>
-      </c>
       <c r="G91">
-        <v>814</v>
+        <v>775</v>
       </c>
       <c r="H91" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I91" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B92" t="s">
         <v>25</v>
@@ -7108,27 +7108,27 @@
         <v>286</v>
       </c>
       <c r="D92" t="s">
+        <v>407</v>
+      </c>
+      <c r="E92" t="s">
         <v>408</v>
       </c>
-      <c r="E92" t="s">
+      <c r="F92" t="s">
         <v>409</v>
       </c>
-      <c r="F92" t="s">
-        <v>410</v>
-      </c>
       <c r="G92">
-        <v>632</v>
+        <v>609</v>
       </c>
       <c r="H92" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I92" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B93" t="s">
         <v>25</v>
@@ -7137,27 +7137,27 @@
         <v>286</v>
       </c>
       <c r="D93" t="s">
+        <v>411</v>
+      </c>
+      <c r="E93" t="s">
         <v>412</v>
       </c>
-      <c r="E93" t="s">
+      <c r="F93" t="s">
         <v>413</v>
       </c>
-      <c r="F93" t="s">
-        <v>414</v>
-      </c>
       <c r="G93">
-        <v>696</v>
+        <v>829</v>
       </c>
       <c r="H93" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I93" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B94" t="s">
         <v>25</v>
@@ -7166,27 +7166,27 @@
         <v>286</v>
       </c>
       <c r="D94" t="s">
+        <v>415</v>
+      </c>
+      <c r="E94" t="s">
         <v>416</v>
       </c>
-      <c r="E94" t="s">
+      <c r="F94" t="s">
         <v>417</v>
       </c>
-      <c r="F94" t="s">
-        <v>418</v>
-      </c>
       <c r="G94">
-        <v>492</v>
+        <v>393</v>
       </c>
       <c r="H94" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I94" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B95" t="s">
         <v>25</v>
@@ -7195,27 +7195,27 @@
         <v>286</v>
       </c>
       <c r="D95" t="s">
+        <v>419</v>
+      </c>
+      <c r="E95" t="s">
         <v>420</v>
       </c>
-      <c r="E95" t="s">
+      <c r="F95" t="s">
         <v>421</v>
       </c>
-      <c r="F95" t="s">
-        <v>422</v>
-      </c>
       <c r="G95">
-        <v>808</v>
+        <v>746</v>
       </c>
       <c r="H95" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I95" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B96" t="s">
         <v>25</v>
@@ -7224,27 +7224,27 @@
         <v>286</v>
       </c>
       <c r="D96" t="s">
+        <v>423</v>
+      </c>
+      <c r="E96" t="s">
         <v>424</v>
       </c>
-      <c r="E96" t="s">
+      <c r="F96" t="s">
         <v>425</v>
       </c>
-      <c r="F96" t="s">
-        <v>426</v>
-      </c>
       <c r="G96">
-        <v>481</v>
+        <v>626</v>
       </c>
       <c r="H96" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I96" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B97" t="s">
         <v>25</v>
@@ -7253,27 +7253,27 @@
         <v>286</v>
       </c>
       <c r="D97" t="s">
+        <v>427</v>
+      </c>
+      <c r="E97" t="s">
         <v>428</v>
       </c>
-      <c r="E97" t="s">
+      <c r="F97" t="s">
         <v>429</v>
       </c>
-      <c r="F97" t="s">
-        <v>430</v>
-      </c>
       <c r="G97">
-        <v>402</v>
+        <v>429</v>
       </c>
       <c r="H97" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I97" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B98" t="s">
         <v>25</v>
@@ -7282,27 +7282,27 @@
         <v>286</v>
       </c>
       <c r="D98" t="s">
+        <v>431</v>
+      </c>
+      <c r="E98" t="s">
         <v>432</v>
       </c>
-      <c r="E98" t="s">
+      <c r="F98" t="s">
         <v>433</v>
       </c>
-      <c r="F98" t="s">
-        <v>434</v>
-      </c>
       <c r="G98">
-        <v>729</v>
+        <v>440</v>
       </c>
       <c r="H98" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I98" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B99" t="s">
         <v>25</v>
@@ -7311,27 +7311,27 @@
         <v>286</v>
       </c>
       <c r="D99" t="s">
+        <v>435</v>
+      </c>
+      <c r="E99" t="s">
         <v>436</v>
       </c>
-      <c r="E99" t="s">
+      <c r="F99" t="s">
         <v>437</v>
       </c>
-      <c r="F99" t="s">
-        <v>438</v>
-      </c>
       <c r="G99">
-        <v>757</v>
+        <v>601</v>
       </c>
       <c r="H99" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I99" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B100" t="s">
         <v>25</v>
@@ -7340,27 +7340,27 @@
         <v>286</v>
       </c>
       <c r="D100" t="s">
+        <v>439</v>
+      </c>
+      <c r="E100" t="s">
         <v>440</v>
       </c>
-      <c r="E100" t="s">
+      <c r="F100" t="s">
         <v>441</v>
       </c>
-      <c r="F100" t="s">
-        <v>442</v>
-      </c>
       <c r="G100">
-        <v>355</v>
+        <v>863</v>
       </c>
       <c r="H100" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I100" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B101" t="s">
         <v>25</v>
@@ -7369,27 +7369,27 @@
         <v>286</v>
       </c>
       <c r="D101" t="s">
+        <v>443</v>
+      </c>
+      <c r="E101" t="s">
         <v>444</v>
       </c>
-      <c r="E101" t="s">
+      <c r="F101" t="s">
         <v>445</v>
       </c>
-      <c r="F101" t="s">
-        <v>446</v>
-      </c>
       <c r="G101">
-        <v>768</v>
+        <v>415</v>
       </c>
       <c r="H101" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I101" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B102" t="s">
         <v>25</v>
@@ -7398,27 +7398,27 @@
         <v>286</v>
       </c>
       <c r="D102" t="s">
+        <v>447</v>
+      </c>
+      <c r="E102" t="s">
         <v>448</v>
       </c>
-      <c r="E102" t="s">
+      <c r="F102" t="s">
         <v>449</v>
       </c>
-      <c r="F102" t="s">
-        <v>450</v>
-      </c>
       <c r="G102">
-        <v>414</v>
+        <v>319</v>
       </c>
       <c r="H102" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I102" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B103" t="s">
         <v>25</v>
@@ -7427,27 +7427,27 @@
         <v>286</v>
       </c>
       <c r="D103" t="s">
+        <v>451</v>
+      </c>
+      <c r="E103" t="s">
         <v>452</v>
       </c>
-      <c r="E103" t="s">
+      <c r="F103" t="s">
         <v>453</v>
       </c>
-      <c r="F103" t="s">
-        <v>454</v>
-      </c>
       <c r="G103">
-        <v>681</v>
+        <v>705</v>
       </c>
       <c r="H103" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I103" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B104" t="s">
         <v>25</v>
@@ -7456,27 +7456,27 @@
         <v>286</v>
       </c>
       <c r="D104" t="s">
+        <v>455</v>
+      </c>
+      <c r="E104" t="s">
         <v>456</v>
       </c>
-      <c r="E104" t="s">
+      <c r="F104" t="s">
         <v>457</v>
       </c>
-      <c r="F104" t="s">
-        <v>458</v>
-      </c>
       <c r="G104">
-        <v>757</v>
+        <v>419</v>
       </c>
       <c r="H104" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I104" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B105" t="s">
         <v>25</v>
@@ -7485,27 +7485,27 @@
         <v>286</v>
       </c>
       <c r="D105" t="s">
+        <v>459</v>
+      </c>
+      <c r="E105" t="s">
         <v>460</v>
       </c>
-      <c r="E105" t="s">
+      <c r="F105" t="s">
         <v>461</v>
       </c>
-      <c r="F105" t="s">
-        <v>462</v>
-      </c>
       <c r="G105">
-        <v>676</v>
+        <v>654</v>
       </c>
       <c r="H105" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I105" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B106" t="s">
         <v>25</v>
@@ -7514,27 +7514,27 @@
         <v>286</v>
       </c>
       <c r="D106" t="s">
+        <v>463</v>
+      </c>
+      <c r="E106" t="s">
         <v>464</v>
       </c>
-      <c r="E106" t="s">
+      <c r="F106" t="s">
         <v>465</v>
       </c>
-      <c r="F106" t="s">
-        <v>466</v>
-      </c>
       <c r="G106">
-        <v>809</v>
+        <v>478</v>
       </c>
       <c r="H106" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I106" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B107" t="s">
         <v>25</v>
@@ -7543,27 +7543,27 @@
         <v>286</v>
       </c>
       <c r="D107" t="s">
+        <v>467</v>
+      </c>
+      <c r="E107" t="s">
         <v>468</v>
       </c>
-      <c r="E107" t="s">
+      <c r="F107" t="s">
         <v>469</v>
       </c>
-      <c r="F107" t="s">
-        <v>470</v>
-      </c>
       <c r="G107">
-        <v>626</v>
+        <v>648</v>
       </c>
       <c r="H107" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I107" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B108" t="s">
         <v>25</v>
@@ -7572,27 +7572,27 @@
         <v>286</v>
       </c>
       <c r="D108" t="s">
+        <v>471</v>
+      </c>
+      <c r="E108" t="s">
         <v>472</v>
       </c>
-      <c r="E108" t="s">
+      <c r="F108" t="s">
         <v>473</v>
       </c>
-      <c r="F108" t="s">
-        <v>474</v>
-      </c>
       <c r="G108">
-        <v>336</v>
+        <v>732</v>
       </c>
       <c r="H108" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I108" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B109" t="s">
         <v>25</v>
@@ -7601,27 +7601,27 @@
         <v>286</v>
       </c>
       <c r="D109" t="s">
+        <v>475</v>
+      </c>
+      <c r="E109" t="s">
         <v>476</v>
       </c>
-      <c r="E109" t="s">
+      <c r="F109" t="s">
         <v>477</v>
       </c>
-      <c r="F109" t="s">
-        <v>478</v>
-      </c>
       <c r="G109">
-        <v>638</v>
+        <v>442</v>
       </c>
       <c r="H109" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I109" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B110" t="s">
         <v>25</v>
@@ -7630,27 +7630,27 @@
         <v>286</v>
       </c>
       <c r="D110" t="s">
+        <v>479</v>
+      </c>
+      <c r="E110" t="s">
         <v>480</v>
       </c>
-      <c r="E110" t="s">
+      <c r="F110" t="s">
         <v>481</v>
       </c>
-      <c r="F110" t="s">
-        <v>482</v>
-      </c>
       <c r="G110">
-        <v>457</v>
+        <v>556</v>
       </c>
       <c r="H110" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I110" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B111" t="s">
         <v>25</v>
@@ -7659,27 +7659,27 @@
         <v>286</v>
       </c>
       <c r="D111" t="s">
+        <v>483</v>
+      </c>
+      <c r="E111" t="s">
         <v>484</v>
       </c>
-      <c r="E111" t="s">
+      <c r="F111" t="s">
         <v>485</v>
       </c>
-      <c r="F111" t="s">
-        <v>486</v>
-      </c>
       <c r="G111">
-        <v>801</v>
+        <v>612</v>
       </c>
       <c r="H111" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I111" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B112" t="s">
         <v>25</v>
@@ -7688,27 +7688,27 @@
         <v>286</v>
       </c>
       <c r="D112" t="s">
+        <v>487</v>
+      </c>
+      <c r="E112" t="s">
         <v>488</v>
       </c>
-      <c r="E112" t="s">
+      <c r="F112" t="s">
         <v>489</v>
       </c>
-      <c r="F112" t="s">
-        <v>490</v>
-      </c>
       <c r="G112">
-        <v>646</v>
+        <v>316</v>
       </c>
       <c r="H112" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I112" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B113" t="s">
         <v>25</v>
@@ -7717,27 +7717,27 @@
         <v>286</v>
       </c>
       <c r="D113" t="s">
+        <v>491</v>
+      </c>
+      <c r="E113" t="s">
         <v>492</v>
       </c>
-      <c r="E113" t="s">
+      <c r="F113" t="s">
         <v>493</v>
       </c>
-      <c r="F113" t="s">
-        <v>494</v>
-      </c>
       <c r="G113">
-        <v>780</v>
+        <v>685</v>
       </c>
       <c r="H113" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I113" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B114" t="s">
         <v>25</v>
@@ -7746,27 +7746,27 @@
         <v>286</v>
       </c>
       <c r="D114" t="s">
+        <v>495</v>
+      </c>
+      <c r="E114" t="s">
         <v>496</v>
       </c>
-      <c r="E114" t="s">
+      <c r="F114" t="s">
         <v>497</v>
       </c>
-      <c r="F114" t="s">
-        <v>498</v>
-      </c>
       <c r="G114">
-        <v>604</v>
+        <v>614</v>
       </c>
       <c r="H114" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I114" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B115" t="s">
         <v>25</v>
@@ -7775,27 +7775,27 @@
         <v>286</v>
       </c>
       <c r="D115" t="s">
+        <v>499</v>
+      </c>
+      <c r="E115" t="s">
         <v>500</v>
       </c>
-      <c r="E115" t="s">
+      <c r="F115" t="s">
         <v>501</v>
       </c>
-      <c r="F115" t="s">
-        <v>502</v>
-      </c>
       <c r="G115">
-        <v>420</v>
+        <v>601</v>
       </c>
       <c r="H115" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I115" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B116" t="s">
         <v>25</v>
@@ -7804,27 +7804,27 @@
         <v>286</v>
       </c>
       <c r="D116" t="s">
+        <v>503</v>
+      </c>
+      <c r="E116" t="s">
         <v>504</v>
       </c>
-      <c r="E116" t="s">
+      <c r="F116" t="s">
         <v>505</v>
       </c>
-      <c r="F116" t="s">
-        <v>506</v>
-      </c>
       <c r="G116">
-        <v>353</v>
+        <v>381</v>
       </c>
       <c r="H116" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I116" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B117" t="s">
         <v>25</v>
@@ -7833,27 +7833,27 @@
         <v>286</v>
       </c>
       <c r="D117" t="s">
+        <v>507</v>
+      </c>
+      <c r="E117" t="s">
         <v>508</v>
       </c>
-      <c r="E117" t="s">
+      <c r="F117" t="s">
         <v>509</v>
       </c>
-      <c r="F117" t="s">
-        <v>510</v>
-      </c>
       <c r="G117">
-        <v>888</v>
+        <v>362</v>
       </c>
       <c r="H117" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I117" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B118" t="s">
         <v>25</v>
@@ -7862,27 +7862,27 @@
         <v>286</v>
       </c>
       <c r="D118" t="s">
+        <v>511</v>
+      </c>
+      <c r="E118" t="s">
         <v>512</v>
       </c>
-      <c r="E118" t="s">
+      <c r="F118" t="s">
         <v>513</v>
       </c>
-      <c r="F118" t="s">
-        <v>514</v>
-      </c>
       <c r="G118">
-        <v>477</v>
+        <v>854</v>
       </c>
       <c r="H118" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I118" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B119" t="s">
         <v>25</v>
@@ -7891,27 +7891,27 @@
         <v>286</v>
       </c>
       <c r="D119" t="s">
+        <v>515</v>
+      </c>
+      <c r="E119" t="s">
         <v>516</v>
       </c>
-      <c r="E119" t="s">
+      <c r="F119" t="s">
         <v>517</v>
       </c>
-      <c r="F119" t="s">
-        <v>518</v>
-      </c>
       <c r="G119">
-        <v>860</v>
+        <v>701</v>
       </c>
       <c r="H119" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I119" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B120" t="s">
         <v>25</v>
@@ -7920,27 +7920,27 @@
         <v>286</v>
       </c>
       <c r="D120" t="s">
+        <v>519</v>
+      </c>
+      <c r="E120" t="s">
         <v>520</v>
       </c>
-      <c r="E120" t="s">
+      <c r="F120" t="s">
         <v>521</v>
       </c>
-      <c r="F120" t="s">
-        <v>522</v>
-      </c>
       <c r="G120">
-        <v>428</v>
+        <v>775</v>
       </c>
       <c r="H120" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I120" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B121" t="s">
         <v>25</v>
@@ -7949,27 +7949,27 @@
         <v>286</v>
       </c>
       <c r="D121" t="s">
+        <v>523</v>
+      </c>
+      <c r="E121" t="s">
         <v>524</v>
       </c>
-      <c r="E121" t="s">
+      <c r="F121" t="s">
         <v>525</v>
       </c>
-      <c r="F121" t="s">
-        <v>526</v>
-      </c>
       <c r="G121">
-        <v>751</v>
+        <v>450</v>
       </c>
       <c r="H121" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I121" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B122" t="s">
         <v>25</v>
@@ -7978,27 +7978,27 @@
         <v>286</v>
       </c>
       <c r="D122" t="s">
+        <v>527</v>
+      </c>
+      <c r="E122" t="s">
         <v>528</v>
       </c>
-      <c r="E122" t="s">
+      <c r="F122" t="s">
         <v>529</v>
       </c>
-      <c r="F122" t="s">
-        <v>530</v>
-      </c>
       <c r="G122">
-        <v>773</v>
+        <v>342</v>
       </c>
       <c r="H122" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I122" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B123" t="s">
         <v>25</v>
@@ -8007,27 +8007,27 @@
         <v>286</v>
       </c>
       <c r="D123" t="s">
+        <v>531</v>
+      </c>
+      <c r="E123" t="s">
         <v>532</v>
       </c>
-      <c r="E123" t="s">
+      <c r="F123" t="s">
         <v>533</v>
       </c>
-      <c r="F123" t="s">
-        <v>534</v>
-      </c>
       <c r="G123">
-        <v>776</v>
+        <v>674</v>
       </c>
       <c r="H123" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I123" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B124" t="s">
         <v>25</v>
@@ -8036,27 +8036,27 @@
         <v>286</v>
       </c>
       <c r="D124" t="s">
+        <v>535</v>
+      </c>
+      <c r="E124" t="s">
         <v>536</v>
       </c>
-      <c r="E124" t="s">
+      <c r="F124" t="s">
         <v>537</v>
       </c>
-      <c r="F124" t="s">
-        <v>538</v>
-      </c>
       <c r="G124">
-        <v>551</v>
+        <v>502</v>
       </c>
       <c r="H124" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I124" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B125" t="s">
         <v>25</v>
@@ -8065,27 +8065,27 @@
         <v>286</v>
       </c>
       <c r="D125" t="s">
+        <v>539</v>
+      </c>
+      <c r="E125" t="s">
         <v>540</v>
       </c>
-      <c r="E125" t="s">
+      <c r="F125" t="s">
         <v>541</v>
       </c>
-      <c r="F125" t="s">
-        <v>542</v>
-      </c>
       <c r="G125">
-        <v>779</v>
+        <v>814</v>
       </c>
       <c r="H125" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I125" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B126" t="s">
         <v>25</v>
@@ -8094,27 +8094,27 @@
         <v>286</v>
       </c>
       <c r="D126" t="s">
+        <v>543</v>
+      </c>
+      <c r="E126" t="s">
         <v>544</v>
       </c>
-      <c r="E126" t="s">
+      <c r="F126" t="s">
         <v>545</v>
       </c>
-      <c r="F126" t="s">
-        <v>546</v>
-      </c>
       <c r="G126">
-        <v>506</v>
+        <v>580</v>
       </c>
       <c r="H126" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I126" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B127" t="s">
         <v>25</v>
@@ -8123,27 +8123,27 @@
         <v>286</v>
       </c>
       <c r="D127" t="s">
+        <v>547</v>
+      </c>
+      <c r="E127" t="s">
         <v>548</v>
       </c>
-      <c r="E127" t="s">
+      <c r="F127" t="s">
         <v>549</v>
       </c>
-      <c r="F127" t="s">
-        <v>550</v>
-      </c>
       <c r="G127">
-        <v>699</v>
+        <v>349</v>
       </c>
       <c r="H127" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I127" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B128" t="s">
         <v>25</v>
@@ -8152,27 +8152,27 @@
         <v>286</v>
       </c>
       <c r="D128" t="s">
+        <v>551</v>
+      </c>
+      <c r="E128" t="s">
         <v>552</v>
       </c>
-      <c r="E128" t="s">
+      <c r="F128" t="s">
         <v>553</v>
       </c>
-      <c r="F128" t="s">
-        <v>554</v>
-      </c>
       <c r="G128">
-        <v>505</v>
+        <v>822</v>
       </c>
       <c r="H128" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I128" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B129" t="s">
         <v>25</v>
@@ -8181,27 +8181,27 @@
         <v>286</v>
       </c>
       <c r="D129" t="s">
+        <v>555</v>
+      </c>
+      <c r="E129" t="s">
         <v>556</v>
       </c>
-      <c r="E129" t="s">
+      <c r="F129" t="s">
         <v>557</v>
       </c>
-      <c r="F129" t="s">
-        <v>558</v>
-      </c>
       <c r="G129">
-        <v>640</v>
+        <v>502</v>
       </c>
       <c r="H129" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I129" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B130" t="s">
         <v>25</v>
@@ -8210,27 +8210,27 @@
         <v>286</v>
       </c>
       <c r="D130" t="s">
+        <v>559</v>
+      </c>
+      <c r="E130" t="s">
         <v>560</v>
       </c>
-      <c r="E130" t="s">
+      <c r="F130" t="s">
         <v>561</v>
       </c>
-      <c r="F130" t="s">
-        <v>562</v>
-      </c>
       <c r="G130">
-        <v>564</v>
+        <v>853</v>
       </c>
       <c r="H130" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I130" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B131" t="s">
         <v>25</v>
@@ -8239,27 +8239,27 @@
         <v>286</v>
       </c>
       <c r="D131" t="s">
+        <v>563</v>
+      </c>
+      <c r="E131" t="s">
         <v>564</v>
       </c>
-      <c r="E131" t="s">
+      <c r="F131" t="s">
         <v>565</v>
       </c>
-      <c r="F131" t="s">
-        <v>566</v>
-      </c>
       <c r="G131">
-        <v>388</v>
+        <v>465</v>
       </c>
       <c r="H131" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I131" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B132" t="s">
         <v>25</v>
@@ -8268,27 +8268,27 @@
         <v>286</v>
       </c>
       <c r="D132" t="s">
+        <v>567</v>
+      </c>
+      <c r="E132" t="s">
         <v>568</v>
       </c>
-      <c r="E132" t="s">
+      <c r="F132" t="s">
         <v>569</v>
       </c>
-      <c r="F132" t="s">
-        <v>570</v>
-      </c>
       <c r="G132">
-        <v>383</v>
+        <v>699</v>
       </c>
       <c r="H132" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I132" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B133" t="s">
         <v>25</v>
@@ -8297,27 +8297,27 @@
         <v>286</v>
       </c>
       <c r="D133" t="s">
+        <v>571</v>
+      </c>
+      <c r="E133" t="s">
         <v>572</v>
       </c>
-      <c r="E133" t="s">
+      <c r="F133" t="s">
         <v>573</v>
       </c>
-      <c r="F133" t="s">
-        <v>574</v>
-      </c>
       <c r="G133">
-        <v>467</v>
+        <v>356</v>
       </c>
       <c r="H133" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I133" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B134" t="s">
         <v>25</v>
@@ -8326,27 +8326,27 @@
         <v>286</v>
       </c>
       <c r="D134" t="s">
+        <v>575</v>
+      </c>
+      <c r="E134" t="s">
         <v>576</v>
       </c>
-      <c r="E134" t="s">
+      <c r="F134" t="s">
         <v>577</v>
       </c>
-      <c r="F134" t="s">
-        <v>578</v>
-      </c>
       <c r="G134">
-        <v>795</v>
+        <v>893</v>
       </c>
       <c r="H134" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I134" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B135" t="s">
         <v>25</v>
@@ -8355,27 +8355,27 @@
         <v>286</v>
       </c>
       <c r="D135" t="s">
+        <v>579</v>
+      </c>
+      <c r="E135" t="s">
         <v>580</v>
       </c>
-      <c r="E135" t="s">
+      <c r="F135" t="s">
         <v>581</v>
       </c>
-      <c r="F135" t="s">
-        <v>582</v>
-      </c>
       <c r="G135">
-        <v>386</v>
+        <v>670</v>
       </c>
       <c r="H135" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I135" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B136" t="s">
         <v>25</v>
@@ -8384,27 +8384,27 @@
         <v>286</v>
       </c>
       <c r="D136" t="s">
+        <v>583</v>
+      </c>
+      <c r="E136" t="s">
         <v>584</v>
       </c>
-      <c r="E136" t="s">
+      <c r="F136" t="s">
         <v>585</v>
       </c>
-      <c r="F136" t="s">
-        <v>586</v>
-      </c>
       <c r="G136">
-        <v>669</v>
+        <v>830</v>
       </c>
       <c r="H136" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I136" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B137" t="s">
         <v>25</v>
@@ -8413,27 +8413,27 @@
         <v>286</v>
       </c>
       <c r="D137" t="s">
+        <v>587</v>
+      </c>
+      <c r="E137" t="s">
         <v>588</v>
       </c>
-      <c r="E137" t="s">
+      <c r="F137" t="s">
         <v>589</v>
       </c>
-      <c r="F137" t="s">
-        <v>590</v>
-      </c>
       <c r="G137">
-        <v>476</v>
+        <v>579</v>
       </c>
       <c r="H137" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I137" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B138" t="s">
         <v>25</v>
@@ -8442,27 +8442,27 @@
         <v>286</v>
       </c>
       <c r="D138" t="s">
+        <v>591</v>
+      </c>
+      <c r="E138" t="s">
         <v>592</v>
       </c>
-      <c r="E138" t="s">
+      <c r="F138" t="s">
         <v>593</v>
       </c>
-      <c r="F138" t="s">
-        <v>594</v>
-      </c>
       <c r="G138">
-        <v>338</v>
+        <v>481</v>
       </c>
       <c r="H138" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I138" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B139" t="s">
         <v>25</v>
@@ -8471,27 +8471,27 @@
         <v>286</v>
       </c>
       <c r="D139" t="s">
+        <v>595</v>
+      </c>
+      <c r="E139" t="s">
         <v>596</v>
       </c>
-      <c r="E139" t="s">
+      <c r="F139" t="s">
         <v>597</v>
       </c>
-      <c r="F139" t="s">
-        <v>598</v>
-      </c>
       <c r="G139">
-        <v>303</v>
+        <v>673</v>
       </c>
       <c r="H139" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I139" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B140" t="s">
         <v>25</v>
@@ -8500,27 +8500,27 @@
         <v>286</v>
       </c>
       <c r="D140" t="s">
+        <v>599</v>
+      </c>
+      <c r="E140" t="s">
         <v>600</v>
       </c>
-      <c r="E140" t="s">
+      <c r="F140" t="s">
         <v>601</v>
       </c>
-      <c r="F140" t="s">
-        <v>602</v>
-      </c>
       <c r="G140">
-        <v>389</v>
+        <v>606</v>
       </c>
       <c r="H140" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I140" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B141" t="s">
         <v>25</v>
@@ -8529,27 +8529,27 @@
         <v>286</v>
       </c>
       <c r="D141" t="s">
+        <v>603</v>
+      </c>
+      <c r="E141" t="s">
         <v>604</v>
       </c>
-      <c r="E141" t="s">
+      <c r="F141" t="s">
         <v>605</v>
       </c>
-      <c r="F141" t="s">
-        <v>606</v>
-      </c>
       <c r="G141">
-        <v>887</v>
+        <v>460</v>
       </c>
       <c r="H141" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I141" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B142" t="s">
         <v>25</v>
@@ -8558,27 +8558,27 @@
         <v>286</v>
       </c>
       <c r="D142" t="s">
+        <v>607</v>
+      </c>
+      <c r="E142" t="s">
         <v>608</v>
       </c>
-      <c r="E142" t="s">
+      <c r="F142" t="s">
         <v>609</v>
       </c>
-      <c r="F142" t="s">
-        <v>610</v>
-      </c>
       <c r="G142">
-        <v>648</v>
+        <v>745</v>
       </c>
       <c r="H142" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I142" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B143" t="s">
         <v>25</v>
@@ -8587,27 +8587,27 @@
         <v>286</v>
       </c>
       <c r="D143" t="s">
+        <v>611</v>
+      </c>
+      <c r="E143" t="s">
         <v>612</v>
       </c>
-      <c r="E143" t="s">
+      <c r="F143" t="s">
         <v>613</v>
       </c>
-      <c r="F143" t="s">
-        <v>614</v>
-      </c>
       <c r="G143">
-        <v>584</v>
+        <v>759</v>
       </c>
       <c r="H143" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I143" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B144" t="s">
         <v>25</v>
@@ -8616,27 +8616,27 @@
         <v>286</v>
       </c>
       <c r="D144" t="s">
+        <v>615</v>
+      </c>
+      <c r="E144" t="s">
         <v>616</v>
       </c>
-      <c r="E144" t="s">
+      <c r="F144" t="s">
         <v>617</v>
       </c>
-      <c r="F144" t="s">
-        <v>618</v>
-      </c>
       <c r="G144">
-        <v>506</v>
+        <v>600</v>
       </c>
       <c r="H144" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I144" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B145" t="s">
         <v>25</v>
@@ -8645,27 +8645,27 @@
         <v>286</v>
       </c>
       <c r="D145" t="s">
+        <v>619</v>
+      </c>
+      <c r="E145" t="s">
         <v>620</v>
       </c>
-      <c r="E145" t="s">
+      <c r="F145" t="s">
         <v>621</v>
       </c>
-      <c r="F145" t="s">
-        <v>622</v>
-      </c>
       <c r="G145">
-        <v>501</v>
+        <v>491</v>
       </c>
       <c r="H145" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I145" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B146" t="s">
         <v>25</v>
@@ -8674,27 +8674,27 @@
         <v>286</v>
       </c>
       <c r="D146" t="s">
+        <v>623</v>
+      </c>
+      <c r="E146" t="s">
         <v>624</v>
       </c>
-      <c r="E146" t="s">
+      <c r="F146" t="s">
         <v>625</v>
       </c>
-      <c r="F146" t="s">
-        <v>626</v>
-      </c>
       <c r="G146">
-        <v>609</v>
+        <v>820</v>
       </c>
       <c r="H146" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I146" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B147" t="s">
         <v>25</v>
@@ -8703,27 +8703,27 @@
         <v>286</v>
       </c>
       <c r="D147" t="s">
+        <v>627</v>
+      </c>
+      <c r="E147" t="s">
         <v>628</v>
       </c>
-      <c r="E147" t="s">
+      <c r="F147" t="s">
         <v>629</v>
       </c>
-      <c r="F147" t="s">
-        <v>630</v>
-      </c>
       <c r="G147">
-        <v>731</v>
+        <v>559</v>
       </c>
       <c r="H147" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I147" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B148" t="s">
         <v>25</v>
@@ -8732,27 +8732,27 @@
         <v>286</v>
       </c>
       <c r="D148" t="s">
+        <v>631</v>
+      </c>
+      <c r="E148" t="s">
         <v>632</v>
       </c>
-      <c r="E148" t="s">
+      <c r="F148" t="s">
         <v>633</v>
       </c>
-      <c r="F148" t="s">
-        <v>634</v>
-      </c>
       <c r="G148">
-        <v>810</v>
+        <v>427</v>
       </c>
       <c r="H148" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I148" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B149" t="s">
         <v>25</v>
@@ -8761,27 +8761,27 @@
         <v>286</v>
       </c>
       <c r="D149" t="s">
+        <v>635</v>
+      </c>
+      <c r="E149" t="s">
         <v>636</v>
       </c>
-      <c r="E149" t="s">
+      <c r="F149" t="s">
         <v>637</v>
       </c>
-      <c r="F149" t="s">
-        <v>638</v>
-      </c>
       <c r="G149">
-        <v>750</v>
+        <v>302</v>
       </c>
       <c r="H149" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I149" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B150" t="s">
         <v>25</v>
@@ -8790,27 +8790,27 @@
         <v>286</v>
       </c>
       <c r="D150" t="s">
+        <v>639</v>
+      </c>
+      <c r="E150" t="s">
         <v>640</v>
       </c>
-      <c r="E150" t="s">
+      <c r="F150" t="s">
         <v>641</v>
       </c>
-      <c r="F150" t="s">
-        <v>642</v>
-      </c>
       <c r="G150">
-        <v>440</v>
+        <v>622</v>
       </c>
       <c r="H150" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I150" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B151" t="s">
         <v>25</v>
@@ -8819,27 +8819,27 @@
         <v>286</v>
       </c>
       <c r="D151" t="s">
+        <v>643</v>
+      </c>
+      <c r="E151" t="s">
         <v>644</v>
       </c>
-      <c r="E151" t="s">
+      <c r="F151" t="s">
         <v>645</v>
       </c>
-      <c r="F151" t="s">
-        <v>646</v>
-      </c>
       <c r="G151">
-        <v>816</v>
+        <v>413</v>
       </c>
       <c r="H151" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I151" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B152" t="s">
         <v>25</v>
@@ -8848,27 +8848,27 @@
         <v>286</v>
       </c>
       <c r="D152" t="s">
+        <v>647</v>
+      </c>
+      <c r="E152" t="s">
         <v>648</v>
       </c>
-      <c r="E152" t="s">
+      <c r="F152" t="s">
         <v>649</v>
       </c>
-      <c r="F152" t="s">
-        <v>650</v>
-      </c>
       <c r="G152">
-        <v>824</v>
+        <v>861</v>
       </c>
       <c r="H152" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I152" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B153" t="s">
         <v>25</v>
@@ -8877,27 +8877,27 @@
         <v>286</v>
       </c>
       <c r="D153" t="s">
+        <v>651</v>
+      </c>
+      <c r="E153" t="s">
         <v>652</v>
       </c>
-      <c r="E153" t="s">
+      <c r="F153" t="s">
         <v>653</v>
       </c>
-      <c r="F153" t="s">
-        <v>654</v>
-      </c>
       <c r="G153">
-        <v>891</v>
+        <v>729</v>
       </c>
       <c r="H153" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I153" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B154" t="s">
         <v>25</v>
@@ -8906,27 +8906,27 @@
         <v>286</v>
       </c>
       <c r="D154" t="s">
+        <v>655</v>
+      </c>
+      <c r="E154" t="s">
         <v>656</v>
       </c>
-      <c r="E154" t="s">
+      <c r="F154" t="s">
         <v>657</v>
       </c>
-      <c r="F154" t="s">
-        <v>658</v>
-      </c>
       <c r="G154">
-        <v>759</v>
+        <v>541</v>
       </c>
       <c r="H154" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I154" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B155" t="s">
         <v>25</v>
@@ -8935,27 +8935,27 @@
         <v>286</v>
       </c>
       <c r="D155" t="s">
+        <v>659</v>
+      </c>
+      <c r="E155" t="s">
         <v>660</v>
       </c>
-      <c r="E155" t="s">
+      <c r="F155" t="s">
         <v>661</v>
       </c>
-      <c r="F155" t="s">
-        <v>662</v>
-      </c>
       <c r="G155">
-        <v>433</v>
+        <v>616</v>
       </c>
       <c r="H155" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I155" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B156" t="s">
         <v>25</v>
@@ -8964,27 +8964,27 @@
         <v>286</v>
       </c>
       <c r="D156" t="s">
+        <v>663</v>
+      </c>
+      <c r="E156" t="s">
         <v>664</v>
       </c>
-      <c r="E156" t="s">
+      <c r="F156" t="s">
         <v>665</v>
       </c>
-      <c r="F156" t="s">
-        <v>666</v>
-      </c>
       <c r="G156">
-        <v>806</v>
+        <v>789</v>
       </c>
       <c r="H156" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I156" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B157" t="s">
         <v>25</v>
@@ -8993,27 +8993,27 @@
         <v>286</v>
       </c>
       <c r="D157" t="s">
+        <v>667</v>
+      </c>
+      <c r="E157" t="s">
         <v>668</v>
       </c>
-      <c r="E157" t="s">
+      <c r="F157" t="s">
         <v>669</v>
       </c>
-      <c r="F157" t="s">
-        <v>670</v>
-      </c>
       <c r="G157">
-        <v>403</v>
+        <v>568</v>
       </c>
       <c r="H157" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I157" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B158" t="s">
         <v>25</v>
@@ -9022,27 +9022,27 @@
         <v>286</v>
       </c>
       <c r="D158" t="s">
+        <v>671</v>
+      </c>
+      <c r="E158" t="s">
         <v>672</v>
       </c>
-      <c r="E158" t="s">
+      <c r="F158" t="s">
         <v>673</v>
       </c>
-      <c r="F158" t="s">
-        <v>674</v>
-      </c>
       <c r="G158">
-        <v>619</v>
+        <v>851</v>
       </c>
       <c r="H158" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I158" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B159" t="s">
         <v>25</v>
@@ -9051,27 +9051,27 @@
         <v>286</v>
       </c>
       <c r="D159" t="s">
+        <v>675</v>
+      </c>
+      <c r="E159" t="s">
         <v>676</v>
       </c>
-      <c r="E159" t="s">
+      <c r="F159" t="s">
         <v>677</v>
       </c>
-      <c r="F159" t="s">
-        <v>678</v>
-      </c>
       <c r="G159">
-        <v>480</v>
+        <v>353</v>
       </c>
       <c r="H159" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I159" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B160" t="s">
         <v>25</v>
@@ -9080,27 +9080,27 @@
         <v>286</v>
       </c>
       <c r="D160" t="s">
+        <v>679</v>
+      </c>
+      <c r="E160" t="s">
         <v>680</v>
       </c>
-      <c r="E160" t="s">
+      <c r="F160" t="s">
         <v>681</v>
       </c>
-      <c r="F160" t="s">
-        <v>682</v>
-      </c>
       <c r="G160">
-        <v>356</v>
+        <v>784</v>
       </c>
       <c r="H160" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I160" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B161" t="s">
         <v>25</v>
@@ -9109,2246 +9109,2246 @@
         <v>286</v>
       </c>
       <c r="D161" t="s">
+        <v>683</v>
+      </c>
+      <c r="E161" t="s">
         <v>684</v>
       </c>
-      <c r="E161" t="s">
+      <c r="F161" t="s">
         <v>685</v>
       </c>
-      <c r="F161" t="s">
-        <v>686</v>
-      </c>
       <c r="G161">
-        <v>526</v>
+        <v>391</v>
       </c>
       <c r="H161" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I161" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B162" t="s">
         <v>27</v>
       </c>
       <c r="C162" t="s">
+        <v>687</v>
+      </c>
+      <c r="D162" t="s">
         <v>688</v>
       </c>
-      <c r="D162" t="s">
+      <c r="E162" t="s">
         <v>689</v>
       </c>
-      <c r="E162" t="s">
+      <c r="F162" t="s">
         <v>690</v>
       </c>
-      <c r="F162" t="s">
-        <v>691</v>
-      </c>
       <c r="G162">
-        <v>230</v>
+        <v>96</v>
       </c>
       <c r="H162" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I162" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B163" t="s">
         <v>27</v>
       </c>
       <c r="C163" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D163" t="s">
+        <v>692</v>
+      </c>
+      <c r="E163" t="s">
         <v>693</v>
       </c>
-      <c r="E163" t="s">
+      <c r="F163" t="s">
         <v>694</v>
       </c>
-      <c r="F163" t="s">
-        <v>695</v>
-      </c>
       <c r="G163">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="H163" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I163" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B164" t="s">
         <v>27</v>
       </c>
       <c r="C164" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D164" t="s">
+        <v>696</v>
+      </c>
+      <c r="E164" t="s">
         <v>697</v>
       </c>
-      <c r="E164" t="s">
+      <c r="F164" t="s">
         <v>698</v>
       </c>
-      <c r="F164" t="s">
-        <v>699</v>
-      </c>
       <c r="G164">
-        <v>171</v>
+        <v>238</v>
       </c>
       <c r="H164" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I164" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B165" t="s">
         <v>27</v>
       </c>
       <c r="C165" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D165" t="s">
+        <v>700</v>
+      </c>
+      <c r="E165" t="s">
         <v>701</v>
       </c>
-      <c r="E165" t="s">
+      <c r="F165" t="s">
         <v>702</v>
       </c>
-      <c r="F165" t="s">
-        <v>703</v>
-      </c>
       <c r="G165">
-        <v>152</v>
+        <v>112</v>
       </c>
       <c r="H165" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I165" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B166" t="s">
         <v>27</v>
       </c>
       <c r="C166" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D166" t="s">
+        <v>704</v>
+      </c>
+      <c r="E166" t="s">
         <v>705</v>
       </c>
-      <c r="E166" t="s">
+      <c r="F166" t="s">
         <v>706</v>
       </c>
-      <c r="F166" t="s">
-        <v>707</v>
-      </c>
       <c r="G166">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="H166" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I166" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B167" t="s">
         <v>27</v>
       </c>
       <c r="C167" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D167" t="s">
+        <v>708</v>
+      </c>
+      <c r="E167" t="s">
         <v>709</v>
       </c>
-      <c r="E167" t="s">
+      <c r="F167" t="s">
         <v>710</v>
       </c>
-      <c r="F167" t="s">
-        <v>711</v>
-      </c>
       <c r="G167">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="H167" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I167" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B168" t="s">
         <v>27</v>
       </c>
       <c r="C168" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D168" t="s">
+        <v>712</v>
+      </c>
+      <c r="E168" t="s">
         <v>713</v>
       </c>
-      <c r="E168" t="s">
+      <c r="F168" t="s">
         <v>714</v>
       </c>
-      <c r="F168" t="s">
-        <v>715</v>
-      </c>
       <c r="G168">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="H168" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I168" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B169" t="s">
         <v>27</v>
       </c>
       <c r="C169" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D169" t="s">
+        <v>716</v>
+      </c>
+      <c r="E169" t="s">
         <v>717</v>
       </c>
-      <c r="E169" t="s">
+      <c r="F169" t="s">
         <v>718</v>
       </c>
-      <c r="F169" t="s">
-        <v>719</v>
-      </c>
       <c r="G169">
-        <v>163</v>
+        <v>66</v>
       </c>
       <c r="H169" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I169" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B170" t="s">
         <v>27</v>
       </c>
       <c r="C170" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D170" t="s">
+        <v>720</v>
+      </c>
+      <c r="E170" t="s">
         <v>721</v>
       </c>
-      <c r="E170" t="s">
+      <c r="F170" t="s">
         <v>722</v>
       </c>
-      <c r="F170" t="s">
-        <v>723</v>
-      </c>
       <c r="G170">
-        <v>182</v>
+        <v>220</v>
       </c>
       <c r="H170" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I170" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B171" t="s">
         <v>27</v>
       </c>
       <c r="C171" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D171" t="s">
+        <v>724</v>
+      </c>
+      <c r="E171" t="s">
         <v>725</v>
       </c>
-      <c r="E171" t="s">
+      <c r="F171" t="s">
         <v>726</v>
       </c>
-      <c r="F171" t="s">
-        <v>727</v>
-      </c>
       <c r="G171">
-        <v>59</v>
+        <v>248</v>
       </c>
       <c r="H171" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I171" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B172" t="s">
         <v>27</v>
       </c>
       <c r="C172" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D172" t="s">
+        <v>728</v>
+      </c>
+      <c r="E172" t="s">
         <v>729</v>
       </c>
-      <c r="E172" t="s">
+      <c r="F172" t="s">
         <v>730</v>
       </c>
-      <c r="F172" t="s">
-        <v>731</v>
-      </c>
       <c r="G172">
-        <v>146</v>
+        <v>77</v>
       </c>
       <c r="H172" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I172" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B173" t="s">
         <v>27</v>
       </c>
       <c r="C173" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D173" t="s">
+        <v>732</v>
+      </c>
+      <c r="E173" t="s">
         <v>733</v>
       </c>
-      <c r="E173" t="s">
+      <c r="F173" t="s">
         <v>734</v>
       </c>
-      <c r="F173" t="s">
-        <v>735</v>
-      </c>
       <c r="G173">
-        <v>163</v>
+        <v>73</v>
       </c>
       <c r="H173" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I173" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B174" t="s">
         <v>27</v>
       </c>
       <c r="C174" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D174" t="s">
+        <v>736</v>
+      </c>
+      <c r="E174" t="s">
         <v>737</v>
       </c>
-      <c r="E174" t="s">
+      <c r="F174" t="s">
         <v>738</v>
       </c>
-      <c r="F174" t="s">
-        <v>739</v>
-      </c>
       <c r="G174">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="H174" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I174" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B175" t="s">
         <v>27</v>
       </c>
       <c r="C175" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D175" t="s">
+        <v>740</v>
+      </c>
+      <c r="E175" t="s">
         <v>741</v>
       </c>
-      <c r="E175" t="s">
+      <c r="F175" t="s">
         <v>742</v>
       </c>
-      <c r="F175" t="s">
-        <v>743</v>
-      </c>
       <c r="G175">
-        <v>247</v>
+        <v>60</v>
       </c>
       <c r="H175" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I175" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B176" t="s">
         <v>27</v>
       </c>
       <c r="C176" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D176" t="s">
+        <v>744</v>
+      </c>
+      <c r="E176" t="s">
         <v>745</v>
       </c>
-      <c r="E176" t="s">
+      <c r="F176" t="s">
         <v>746</v>
       </c>
-      <c r="F176" t="s">
-        <v>747</v>
-      </c>
       <c r="G176">
-        <v>241</v>
+        <v>156</v>
       </c>
       <c r="H176" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I176" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B177" t="s">
         <v>27</v>
       </c>
       <c r="C177" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D177" t="s">
+        <v>748</v>
+      </c>
+      <c r="E177" t="s">
         <v>749</v>
       </c>
-      <c r="E177" t="s">
+      <c r="F177" t="s">
         <v>750</v>
       </c>
-      <c r="F177" t="s">
-        <v>751</v>
-      </c>
       <c r="G177">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="H177" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I177" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B178" t="s">
         <v>27</v>
       </c>
       <c r="C178" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D178" t="s">
+        <v>752</v>
+      </c>
+      <c r="E178" t="s">
         <v>753</v>
       </c>
-      <c r="E178" t="s">
+      <c r="F178" t="s">
         <v>754</v>
       </c>
-      <c r="F178" t="s">
-        <v>755</v>
-      </c>
       <c r="G178">
-        <v>184</v>
+        <v>224</v>
       </c>
       <c r="H178" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I178" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B179" t="s">
         <v>27</v>
       </c>
       <c r="C179" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D179" t="s">
+        <v>756</v>
+      </c>
+      <c r="E179" t="s">
         <v>757</v>
       </c>
-      <c r="E179" t="s">
+      <c r="F179" t="s">
         <v>758</v>
       </c>
-      <c r="F179" t="s">
-        <v>759</v>
-      </c>
       <c r="G179">
-        <v>74</v>
+        <v>111</v>
       </c>
       <c r="H179" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I179" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B180" t="s">
         <v>27</v>
       </c>
       <c r="C180" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D180" t="s">
+        <v>760</v>
+      </c>
+      <c r="E180" t="s">
         <v>761</v>
       </c>
-      <c r="E180" t="s">
+      <c r="F180" t="s">
         <v>762</v>
       </c>
-      <c r="F180" t="s">
-        <v>763</v>
-      </c>
       <c r="G180">
-        <v>75</v>
+        <v>149</v>
       </c>
       <c r="H180" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I180" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B181" t="s">
         <v>27</v>
       </c>
       <c r="C181" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D181" t="s">
+        <v>764</v>
+      </c>
+      <c r="E181" t="s">
         <v>765</v>
       </c>
-      <c r="E181" t="s">
+      <c r="F181" t="s">
         <v>766</v>
       </c>
-      <c r="F181" t="s">
-        <v>767</v>
-      </c>
       <c r="G181">
-        <v>163</v>
+        <v>111</v>
       </c>
       <c r="H181" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I181" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B182" t="s">
         <v>27</v>
       </c>
       <c r="C182" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D182" t="s">
+        <v>768</v>
+      </c>
+      <c r="E182" t="s">
         <v>769</v>
       </c>
-      <c r="E182" t="s">
+      <c r="F182" t="s">
         <v>770</v>
       </c>
-      <c r="F182" t="s">
-        <v>771</v>
-      </c>
       <c r="G182">
-        <v>89</v>
+        <v>161</v>
       </c>
       <c r="H182" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I182" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B183" t="s">
         <v>27</v>
       </c>
       <c r="C183" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D183" t="s">
+        <v>772</v>
+      </c>
+      <c r="E183" t="s">
         <v>773</v>
       </c>
-      <c r="E183" t="s">
+      <c r="F183" t="s">
         <v>774</v>
       </c>
-      <c r="F183" t="s">
-        <v>775</v>
-      </c>
       <c r="G183">
-        <v>153</v>
+        <v>196</v>
       </c>
       <c r="H183" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I183" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B184" t="s">
         <v>27</v>
       </c>
       <c r="C184" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D184" t="s">
+        <v>776</v>
+      </c>
+      <c r="E184" t="s">
         <v>777</v>
       </c>
-      <c r="E184" t="s">
+      <c r="F184" t="s">
         <v>778</v>
       </c>
-      <c r="F184" t="s">
-        <v>779</v>
-      </c>
       <c r="G184">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="H184" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I184" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B185" t="s">
         <v>27</v>
       </c>
       <c r="C185" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D185" t="s">
+        <v>780</v>
+      </c>
+      <c r="E185" t="s">
         <v>781</v>
       </c>
-      <c r="E185" t="s">
+      <c r="F185" t="s">
         <v>782</v>
       </c>
-      <c r="F185" t="s">
-        <v>783</v>
-      </c>
       <c r="G185">
-        <v>222</v>
+        <v>171</v>
       </c>
       <c r="H185" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I185" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B186" t="s">
         <v>27</v>
       </c>
       <c r="C186" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D186" t="s">
+        <v>784</v>
+      </c>
+      <c r="E186" t="s">
         <v>785</v>
       </c>
-      <c r="E186" t="s">
+      <c r="F186" t="s">
         <v>786</v>
       </c>
-      <c r="F186" t="s">
-        <v>787</v>
-      </c>
       <c r="G186">
-        <v>163</v>
+        <v>204</v>
       </c>
       <c r="H186" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I186" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B187" t="s">
         <v>27</v>
       </c>
       <c r="C187" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D187" t="s">
+        <v>788</v>
+      </c>
+      <c r="E187" t="s">
         <v>789</v>
       </c>
-      <c r="E187" t="s">
+      <c r="F187" t="s">
         <v>790</v>
       </c>
-      <c r="F187" t="s">
-        <v>791</v>
-      </c>
       <c r="G187">
-        <v>249</v>
+        <v>200</v>
       </c>
       <c r="H187" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I187" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B188" t="s">
         <v>27</v>
       </c>
       <c r="C188" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D188" t="s">
+        <v>792</v>
+      </c>
+      <c r="E188" t="s">
         <v>793</v>
       </c>
-      <c r="E188" t="s">
+      <c r="F188" t="s">
         <v>794</v>
       </c>
-      <c r="F188" t="s">
-        <v>795</v>
-      </c>
       <c r="G188">
-        <v>120</v>
+        <v>63</v>
       </c>
       <c r="H188" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I188" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="B189" t="s">
         <v>27</v>
       </c>
       <c r="C189" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D189" t="s">
+        <v>796</v>
+      </c>
+      <c r="E189" t="s">
         <v>797</v>
       </c>
-      <c r="E189" t="s">
+      <c r="F189" t="s">
         <v>798</v>
       </c>
-      <c r="F189" t="s">
-        <v>799</v>
-      </c>
       <c r="G189">
-        <v>246</v>
+        <v>141</v>
       </c>
       <c r="H189" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I189" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B190" t="s">
         <v>27</v>
       </c>
       <c r="C190" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D190" t="s">
+        <v>800</v>
+      </c>
+      <c r="E190" t="s">
         <v>801</v>
       </c>
-      <c r="E190" t="s">
+      <c r="F190" t="s">
         <v>802</v>
       </c>
-      <c r="F190" t="s">
-        <v>803</v>
-      </c>
       <c r="G190">
-        <v>231</v>
+        <v>206</v>
       </c>
       <c r="H190" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I190" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B191" t="s">
         <v>27</v>
       </c>
       <c r="C191" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D191" t="s">
+        <v>804</v>
+      </c>
+      <c r="E191" t="s">
         <v>805</v>
       </c>
-      <c r="E191" t="s">
+      <c r="F191" t="s">
         <v>806</v>
       </c>
-      <c r="F191" t="s">
-        <v>807</v>
-      </c>
       <c r="G191">
-        <v>50</v>
+        <v>235</v>
       </c>
       <c r="H191" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I191" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B192" t="s">
         <v>27</v>
       </c>
       <c r="C192" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D192" t="s">
+        <v>808</v>
+      </c>
+      <c r="E192" t="s">
         <v>809</v>
       </c>
-      <c r="E192" t="s">
+      <c r="F192" t="s">
         <v>810</v>
       </c>
-      <c r="F192" t="s">
-        <v>811</v>
-      </c>
       <c r="G192">
-        <v>115</v>
+        <v>221</v>
       </c>
       <c r="H192" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I192" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B193" t="s">
         <v>27</v>
       </c>
       <c r="C193" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D193" t="s">
+        <v>812</v>
+      </c>
+      <c r="E193" t="s">
         <v>813</v>
       </c>
-      <c r="E193" t="s">
+      <c r="F193" t="s">
         <v>814</v>
       </c>
-      <c r="F193" t="s">
-        <v>815</v>
-      </c>
       <c r="G193">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="H193" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I193" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B194" t="s">
         <v>27</v>
       </c>
       <c r="C194" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D194" t="s">
+        <v>816</v>
+      </c>
+      <c r="E194" t="s">
         <v>817</v>
       </c>
-      <c r="E194" t="s">
+      <c r="F194" t="s">
         <v>818</v>
       </c>
-      <c r="F194" t="s">
-        <v>819</v>
-      </c>
       <c r="G194">
-        <v>227</v>
+        <v>164</v>
       </c>
       <c r="H194" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I194" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B195" t="s">
         <v>27</v>
       </c>
       <c r="C195" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D195" t="s">
+        <v>820</v>
+      </c>
+      <c r="E195" t="s">
         <v>821</v>
       </c>
-      <c r="E195" t="s">
+      <c r="F195" t="s">
         <v>822</v>
       </c>
-      <c r="F195" t="s">
-        <v>823</v>
-      </c>
       <c r="G195">
-        <v>195</v>
+        <v>111</v>
       </c>
       <c r="H195" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I195" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B196" t="s">
         <v>27</v>
       </c>
       <c r="C196" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D196" t="s">
+        <v>824</v>
+      </c>
+      <c r="E196" t="s">
         <v>825</v>
       </c>
-      <c r="E196" t="s">
+      <c r="F196" t="s">
         <v>826</v>
       </c>
-      <c r="F196" t="s">
-        <v>827</v>
-      </c>
       <c r="G196">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="H196" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I196" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="B197" t="s">
         <v>27</v>
       </c>
       <c r="C197" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D197" t="s">
+        <v>828</v>
+      </c>
+      <c r="E197" t="s">
         <v>829</v>
       </c>
-      <c r="E197" t="s">
+      <c r="F197" t="s">
         <v>830</v>
       </c>
-      <c r="F197" t="s">
-        <v>831</v>
-      </c>
       <c r="G197">
-        <v>171</v>
+        <v>119</v>
       </c>
       <c r="H197" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I197" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B198" t="s">
         <v>27</v>
       </c>
       <c r="C198" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D198" t="s">
+        <v>832</v>
+      </c>
+      <c r="E198" t="s">
         <v>833</v>
       </c>
-      <c r="E198" t="s">
+      <c r="F198" t="s">
         <v>834</v>
       </c>
-      <c r="F198" t="s">
-        <v>835</v>
-      </c>
       <c r="G198">
-        <v>132</v>
+        <v>245</v>
       </c>
       <c r="H198" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I198" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="B199" t="s">
         <v>27</v>
       </c>
       <c r="C199" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D199" t="s">
+        <v>836</v>
+      </c>
+      <c r="E199" t="s">
         <v>837</v>
       </c>
-      <c r="E199" t="s">
+      <c r="F199" t="s">
         <v>838</v>
       </c>
-      <c r="F199" t="s">
-        <v>839</v>
-      </c>
       <c r="G199">
-        <v>245</v>
+        <v>75</v>
       </c>
       <c r="H199" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I199" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="B200" t="s">
         <v>27</v>
       </c>
       <c r="C200" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D200" t="s">
+        <v>840</v>
+      </c>
+      <c r="E200" t="s">
         <v>841</v>
       </c>
-      <c r="E200" t="s">
+      <c r="F200" t="s">
         <v>842</v>
       </c>
-      <c r="F200" t="s">
-        <v>843</v>
-      </c>
       <c r="G200">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="H200" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I200" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B201" t="s">
         <v>27</v>
       </c>
       <c r="C201" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D201" t="s">
+        <v>844</v>
+      </c>
+      <c r="E201" t="s">
         <v>845</v>
       </c>
-      <c r="E201" t="s">
+      <c r="F201" t="s">
         <v>846</v>
       </c>
-      <c r="F201" t="s">
-        <v>847</v>
-      </c>
       <c r="G201">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="H201" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I201" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B202" t="s">
         <v>27</v>
       </c>
       <c r="C202" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D202" t="s">
+        <v>848</v>
+      </c>
+      <c r="E202" t="s">
         <v>849</v>
       </c>
-      <c r="E202" t="s">
+      <c r="F202" t="s">
         <v>850</v>
       </c>
-      <c r="F202" t="s">
-        <v>851</v>
-      </c>
       <c r="G202">
-        <v>93</v>
+        <v>234</v>
       </c>
       <c r="H202" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I202" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="B203" t="s">
         <v>27</v>
       </c>
       <c r="C203" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D203" t="s">
+        <v>852</v>
+      </c>
+      <c r="E203" t="s">
         <v>853</v>
       </c>
-      <c r="E203" t="s">
+      <c r="F203" t="s">
         <v>854</v>
       </c>
-      <c r="F203" t="s">
-        <v>855</v>
-      </c>
       <c r="G203">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H203" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I203" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B204" t="s">
         <v>27</v>
       </c>
       <c r="C204" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D204" t="s">
+        <v>856</v>
+      </c>
+      <c r="E204" t="s">
         <v>857</v>
       </c>
-      <c r="E204" t="s">
+      <c r="F204" t="s">
         <v>858</v>
       </c>
-      <c r="F204" t="s">
-        <v>859</v>
-      </c>
       <c r="G204">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="H204" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I204" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="B205" t="s">
         <v>27</v>
       </c>
       <c r="C205" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D205" t="s">
+        <v>860</v>
+      </c>
+      <c r="E205" t="s">
         <v>861</v>
       </c>
-      <c r="E205" t="s">
+      <c r="F205" t="s">
         <v>862</v>
       </c>
-      <c r="F205" t="s">
-        <v>863</v>
-      </c>
       <c r="G205">
-        <v>159</v>
+        <v>234</v>
       </c>
       <c r="H205" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I205" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B206" t="s">
         <v>27</v>
       </c>
       <c r="C206" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D206" t="s">
+        <v>864</v>
+      </c>
+      <c r="E206" t="s">
         <v>865</v>
       </c>
-      <c r="E206" t="s">
+      <c r="F206" t="s">
         <v>866</v>
       </c>
-      <c r="F206" t="s">
-        <v>867</v>
-      </c>
       <c r="G206">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="H206" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I206" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B207" t="s">
         <v>27</v>
       </c>
       <c r="C207" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D207" t="s">
+        <v>868</v>
+      </c>
+      <c r="E207" t="s">
         <v>869</v>
       </c>
-      <c r="E207" t="s">
+      <c r="F207" t="s">
         <v>870</v>
       </c>
-      <c r="F207" t="s">
-        <v>871</v>
-      </c>
       <c r="G207">
-        <v>168</v>
+        <v>222</v>
       </c>
       <c r="H207" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I207" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="B208" t="s">
         <v>27</v>
       </c>
       <c r="C208" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D208" t="s">
+        <v>872</v>
+      </c>
+      <c r="E208" t="s">
         <v>873</v>
       </c>
-      <c r="E208" t="s">
+      <c r="F208" t="s">
         <v>874</v>
       </c>
-      <c r="F208" t="s">
-        <v>875</v>
-      </c>
       <c r="G208">
-        <v>245</v>
+        <v>158</v>
       </c>
       <c r="H208" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I208" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B209" t="s">
         <v>27</v>
       </c>
       <c r="C209" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D209" t="s">
+        <v>876</v>
+      </c>
+      <c r="E209" t="s">
         <v>877</v>
       </c>
-      <c r="E209" t="s">
+      <c r="F209" t="s">
         <v>878</v>
       </c>
-      <c r="F209" t="s">
-        <v>879</v>
-      </c>
       <c r="G209">
-        <v>206</v>
+        <v>151</v>
       </c>
       <c r="H209" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I209" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B210" t="s">
         <v>27</v>
       </c>
       <c r="C210" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D210" t="s">
+        <v>880</v>
+      </c>
+      <c r="E210" t="s">
         <v>881</v>
       </c>
-      <c r="E210" t="s">
+      <c r="F210" t="s">
         <v>882</v>
       </c>
-      <c r="F210" t="s">
-        <v>883</v>
-      </c>
       <c r="G210">
-        <v>145</v>
+        <v>230</v>
       </c>
       <c r="H210" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I210" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B211" t="s">
         <v>27</v>
       </c>
       <c r="C211" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D211" t="s">
+        <v>884</v>
+      </c>
+      <c r="E211" t="s">
         <v>885</v>
       </c>
-      <c r="E211" t="s">
+      <c r="F211" t="s">
         <v>886</v>
       </c>
-      <c r="F211" t="s">
-        <v>887</v>
-      </c>
       <c r="G211">
-        <v>75</v>
+        <v>156</v>
       </c>
       <c r="H211" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I211" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="B212" t="s">
         <v>27</v>
       </c>
       <c r="C212" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D212" t="s">
+        <v>888</v>
+      </c>
+      <c r="E212" t="s">
         <v>889</v>
       </c>
-      <c r="E212" t="s">
+      <c r="F212" t="s">
         <v>890</v>
       </c>
-      <c r="F212" t="s">
-        <v>891</v>
-      </c>
       <c r="G212">
-        <v>145</v>
+        <v>88</v>
       </c>
       <c r="H212" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I212" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="B213" t="s">
         <v>27</v>
       </c>
       <c r="C213" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D213" t="s">
+        <v>892</v>
+      </c>
+      <c r="E213" t="s">
         <v>893</v>
       </c>
-      <c r="E213" t="s">
+      <c r="F213" t="s">
         <v>894</v>
       </c>
-      <c r="F213" t="s">
-        <v>895</v>
-      </c>
       <c r="G213">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="H213" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I213" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="B214" t="s">
         <v>27</v>
       </c>
       <c r="C214" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D214" t="s">
+        <v>896</v>
+      </c>
+      <c r="E214" t="s">
         <v>897</v>
       </c>
-      <c r="E214" t="s">
+      <c r="F214" t="s">
         <v>898</v>
       </c>
-      <c r="F214" t="s">
-        <v>899</v>
-      </c>
       <c r="G214">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H214" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I214" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B215" t="s">
         <v>27</v>
       </c>
       <c r="C215" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D215" t="s">
+        <v>900</v>
+      </c>
+      <c r="E215" t="s">
         <v>901</v>
       </c>
-      <c r="E215" t="s">
+      <c r="F215" t="s">
         <v>902</v>
       </c>
-      <c r="F215" t="s">
-        <v>903</v>
-      </c>
       <c r="G215">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="H215" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I215" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B216" t="s">
         <v>27</v>
       </c>
       <c r="C216" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D216" t="s">
+        <v>904</v>
+      </c>
+      <c r="E216" t="s">
         <v>905</v>
       </c>
-      <c r="E216" t="s">
+      <c r="F216" t="s">
         <v>906</v>
       </c>
-      <c r="F216" t="s">
-        <v>907</v>
-      </c>
       <c r="G216">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="H216" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I216" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="B217" t="s">
         <v>27</v>
       </c>
       <c r="C217" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D217" t="s">
+        <v>908</v>
+      </c>
+      <c r="E217" t="s">
         <v>909</v>
       </c>
-      <c r="E217" t="s">
+      <c r="F217" t="s">
         <v>910</v>
       </c>
-      <c r="F217" t="s">
-        <v>911</v>
-      </c>
       <c r="G217">
-        <v>157</v>
+        <v>223</v>
       </c>
       <c r="H217" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I217" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="B218" t="s">
         <v>27</v>
       </c>
       <c r="C218" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D218" t="s">
+        <v>912</v>
+      </c>
+      <c r="E218" t="s">
         <v>913</v>
       </c>
-      <c r="E218" t="s">
+      <c r="F218" t="s">
         <v>914</v>
       </c>
-      <c r="F218" t="s">
-        <v>915</v>
-      </c>
       <c r="G218">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="H218" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I218" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="B219" t="s">
         <v>27</v>
       </c>
       <c r="C219" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D219" t="s">
+        <v>916</v>
+      </c>
+      <c r="E219" t="s">
         <v>917</v>
       </c>
-      <c r="E219" t="s">
+      <c r="F219" t="s">
         <v>918</v>
       </c>
-      <c r="F219" t="s">
-        <v>919</v>
-      </c>
       <c r="G219">
-        <v>141</v>
+        <v>108</v>
       </c>
       <c r="H219" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I219" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="B220" t="s">
         <v>27</v>
       </c>
       <c r="C220" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D220" t="s">
+        <v>920</v>
+      </c>
+      <c r="E220" t="s">
         <v>921</v>
       </c>
-      <c r="E220" t="s">
+      <c r="F220" t="s">
         <v>922</v>
       </c>
-      <c r="F220" t="s">
-        <v>923</v>
-      </c>
       <c r="G220">
-        <v>129</v>
+        <v>68</v>
       </c>
       <c r="H220" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I220" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="B221" t="s">
         <v>27</v>
       </c>
       <c r="C221" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D221" t="s">
+        <v>924</v>
+      </c>
+      <c r="E221" t="s">
         <v>925</v>
       </c>
-      <c r="E221" t="s">
+      <c r="F221" t="s">
         <v>926</v>
       </c>
-      <c r="F221" t="s">
-        <v>927</v>
-      </c>
       <c r="G221">
-        <v>150</v>
+        <v>249</v>
       </c>
       <c r="H221" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I221" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="B222" t="s">
         <v>29</v>
       </c>
       <c r="C222" t="s">
+        <v>928</v>
+      </c>
+      <c r="D222" t="s">
         <v>929</v>
       </c>
-      <c r="D222" t="s">
+      <c r="E222" t="s">
         <v>930</v>
       </c>
-      <c r="E222" t="s">
+      <c r="F222" t="s">
         <v>931</v>
       </c>
-      <c r="F222" t="s">
-        <v>932</v>
-      </c>
       <c r="G222">
-        <v>248</v>
+        <v>589</v>
       </c>
       <c r="H222" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I222" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="B223" t="s">
         <v>29</v>
       </c>
       <c r="C223" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D223" t="s">
+        <v>933</v>
+      </c>
+      <c r="E223" t="s">
         <v>934</v>
       </c>
-      <c r="E223" t="s">
+      <c r="F223" t="s">
         <v>935</v>
       </c>
-      <c r="F223" t="s">
-        <v>936</v>
-      </c>
       <c r="G223">
-        <v>496</v>
+        <v>339</v>
       </c>
       <c r="H223" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I223" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="B224" t="s">
         <v>29</v>
       </c>
       <c r="C224" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D224" t="s">
+        <v>937</v>
+      </c>
+      <c r="E224" t="s">
         <v>938</v>
       </c>
-      <c r="E224" t="s">
+      <c r="F224" t="s">
         <v>939</v>
       </c>
-      <c r="F224" t="s">
-        <v>940</v>
-      </c>
       <c r="G224">
-        <v>411</v>
+        <v>255</v>
       </c>
       <c r="H224" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I224" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B225" t="s">
         <v>29</v>
       </c>
       <c r="C225" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D225" t="s">
+        <v>941</v>
+      </c>
+      <c r="E225" t="s">
         <v>942</v>
       </c>
-      <c r="E225" t="s">
+      <c r="F225" t="s">
         <v>943</v>
       </c>
-      <c r="F225" t="s">
-        <v>944</v>
-      </c>
       <c r="G225">
-        <v>357</v>
+        <v>529</v>
       </c>
       <c r="H225" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I225" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="B226" t="s">
         <v>29</v>
       </c>
       <c r="C226" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D226" t="s">
+        <v>945</v>
+      </c>
+      <c r="E226" t="s">
         <v>946</v>
       </c>
-      <c r="E226" t="s">
+      <c r="F226" t="s">
         <v>947</v>
       </c>
-      <c r="F226" t="s">
-        <v>948</v>
-      </c>
       <c r="G226">
-        <v>514</v>
+        <v>537</v>
       </c>
       <c r="H226" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I226" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="B227" t="s">
         <v>29</v>
       </c>
       <c r="C227" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D227" t="s">
+        <v>949</v>
+      </c>
+      <c r="E227" t="s">
         <v>950</v>
       </c>
-      <c r="E227" t="s">
+      <c r="F227" t="s">
         <v>951</v>
       </c>
-      <c r="F227" t="s">
-        <v>952</v>
-      </c>
       <c r="G227">
-        <v>375</v>
+        <v>440</v>
       </c>
       <c r="H227" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I227" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B228" t="s">
         <v>29</v>
       </c>
       <c r="C228" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D228" t="s">
+        <v>953</v>
+      </c>
+      <c r="E228" t="s">
         <v>954</v>
       </c>
-      <c r="E228" t="s">
+      <c r="F228" t="s">
         <v>955</v>
       </c>
-      <c r="F228" t="s">
-        <v>956</v>
-      </c>
       <c r="G228">
-        <v>302</v>
+        <v>638</v>
       </c>
       <c r="H228" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I228" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="B229" t="s">
         <v>29</v>
       </c>
       <c r="C229" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D229" t="s">
+        <v>957</v>
+      </c>
+      <c r="E229" t="s">
         <v>958</v>
       </c>
-      <c r="E229" t="s">
+      <c r="F229" t="s">
         <v>959</v>
       </c>
-      <c r="F229" t="s">
-        <v>960</v>
-      </c>
       <c r="G229">
-        <v>413</v>
+        <v>563</v>
       </c>
       <c r="H229" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I229" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="B230" t="s">
         <v>29</v>
       </c>
       <c r="C230" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D230" t="s">
+        <v>961</v>
+      </c>
+      <c r="E230" t="s">
         <v>962</v>
       </c>
-      <c r="E230" t="s">
+      <c r="F230" t="s">
         <v>963</v>
       </c>
-      <c r="F230" t="s">
-        <v>964</v>
-      </c>
       <c r="G230">
-        <v>464</v>
+        <v>218</v>
       </c>
       <c r="H230" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I230" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B231" t="s">
         <v>29</v>
       </c>
       <c r="C231" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D231" t="s">
+        <v>965</v>
+      </c>
+      <c r="E231" t="s">
         <v>966</v>
       </c>
-      <c r="E231" t="s">
+      <c r="F231" t="s">
         <v>967</v>
       </c>
-      <c r="F231" t="s">
-        <v>968</v>
-      </c>
       <c r="G231">
-        <v>463</v>
+        <v>489</v>
       </c>
       <c r="H231" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I231" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B232" t="s">
         <v>29</v>
       </c>
       <c r="C232" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D232" t="s">
+        <v>969</v>
+      </c>
+      <c r="E232" t="s">
         <v>970</v>
       </c>
-      <c r="E232" t="s">
+      <c r="F232" t="s">
         <v>971</v>
       </c>
-      <c r="F232" t="s">
-        <v>972</v>
-      </c>
       <c r="G232">
-        <v>348</v>
+        <v>274</v>
       </c>
       <c r="H232" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I232" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="B233" t="s">
         <v>29</v>
       </c>
       <c r="C233" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D233" t="s">
+        <v>973</v>
+      </c>
+      <c r="E233" t="s">
         <v>974</v>
       </c>
-      <c r="E233" t="s">
+      <c r="F233" t="s">
         <v>975</v>
       </c>
-      <c r="F233" t="s">
-        <v>976</v>
-      </c>
       <c r="G233">
-        <v>354</v>
+        <v>466</v>
       </c>
       <c r="H233" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I233" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="B234" t="s">
         <v>29</v>
       </c>
       <c r="C234" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D234" t="s">
+        <v>977</v>
+      </c>
+      <c r="E234" t="s">
         <v>978</v>
       </c>
-      <c r="E234" t="s">
+      <c r="F234" t="s">
         <v>979</v>
       </c>
-      <c r="F234" t="s">
-        <v>980</v>
-      </c>
       <c r="G234">
-        <v>376</v>
+        <v>535</v>
       </c>
       <c r="H234" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I234" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="B235" t="s">
         <v>29</v>
       </c>
       <c r="C235" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D235" t="s">
+        <v>981</v>
+      </c>
+      <c r="E235" t="s">
         <v>982</v>
       </c>
-      <c r="E235" t="s">
+      <c r="F235" t="s">
         <v>983</v>
       </c>
-      <c r="F235" t="s">
-        <v>984</v>
-      </c>
       <c r="G235">
-        <v>511</v>
+        <v>587</v>
       </c>
       <c r="H235" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I235" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="B236" t="s">
         <v>29</v>
       </c>
       <c r="C236" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D236" t="s">
+        <v>985</v>
+      </c>
+      <c r="E236" t="s">
         <v>986</v>
       </c>
-      <c r="E236" t="s">
+      <c r="F236" t="s">
         <v>987</v>
       </c>
-      <c r="F236" t="s">
-        <v>988</v>
-      </c>
       <c r="G236">
-        <v>547</v>
+        <v>536</v>
       </c>
       <c r="H236" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I236" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="B237" t="s">
         <v>29</v>
       </c>
       <c r="C237" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D237" t="s">
+        <v>989</v>
+      </c>
+      <c r="E237" t="s">
         <v>990</v>
       </c>
-      <c r="E237" t="s">
+      <c r="F237" t="s">
         <v>991</v>
       </c>
-      <c r="F237" t="s">
-        <v>992</v>
-      </c>
       <c r="G237">
-        <v>556</v>
+        <v>386</v>
       </c>
       <c r="H237" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I237" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="B238" t="s">
         <v>29</v>
       </c>
       <c r="C238" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D238" t="s">
+        <v>993</v>
+      </c>
+      <c r="E238" t="s">
         <v>994</v>
       </c>
-      <c r="E238" t="s">
+      <c r="F238" t="s">
         <v>995</v>
-      </c>
-      <c r="F238" t="s">
-        <v>996</v>
       </c>
       <c r="G238">
         <v>239</v>
@@ -11357,1457 +11357,1457 @@
         <v>46</v>
       </c>
       <c r="I238" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="B239" t="s">
         <v>29</v>
       </c>
       <c r="C239" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D239" t="s">
+        <v>997</v>
+      </c>
+      <c r="E239" t="s">
         <v>998</v>
       </c>
-      <c r="E239" t="s">
+      <c r="F239" t="s">
         <v>999</v>
       </c>
-      <c r="F239" t="s">
-        <v>1000</v>
-      </c>
       <c r="G239">
-        <v>636</v>
+        <v>451</v>
       </c>
       <c r="H239" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I239" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B240" t="s">
         <v>29</v>
       </c>
       <c r="C240" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D240" t="s">
+        <v>1001</v>
+      </c>
+      <c r="E240" t="s">
         <v>1002</v>
       </c>
-      <c r="E240" t="s">
+      <c r="F240" t="s">
         <v>1003</v>
       </c>
-      <c r="F240" t="s">
-        <v>1004</v>
-      </c>
       <c r="G240">
-        <v>628</v>
+        <v>241</v>
       </c>
       <c r="H240" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I240" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B241" t="s">
         <v>29</v>
       </c>
       <c r="C241" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D241" t="s">
+        <v>1005</v>
+      </c>
+      <c r="E241" t="s">
         <v>1006</v>
       </c>
-      <c r="E241" t="s">
+      <c r="F241" t="s">
         <v>1007</v>
       </c>
-      <c r="F241" t="s">
-        <v>1008</v>
-      </c>
       <c r="G241">
-        <v>250</v>
+        <v>315</v>
       </c>
       <c r="H241" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I241" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B242" t="s">
         <v>29</v>
       </c>
       <c r="C242" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D242" t="s">
+        <v>1009</v>
+      </c>
+      <c r="E242" t="s">
         <v>1010</v>
       </c>
-      <c r="E242" t="s">
+      <c r="F242" t="s">
         <v>1011</v>
       </c>
-      <c r="F242" t="s">
-        <v>1012</v>
-      </c>
       <c r="G242">
-        <v>431</v>
+        <v>324</v>
       </c>
       <c r="H242" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I242" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B243" t="s">
         <v>29</v>
       </c>
       <c r="C243" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D243" t="s">
+        <v>1013</v>
+      </c>
+      <c r="E243" t="s">
         <v>1014</v>
       </c>
-      <c r="E243" t="s">
+      <c r="F243" t="s">
         <v>1015</v>
       </c>
-      <c r="F243" t="s">
-        <v>1016</v>
-      </c>
       <c r="G243">
-        <v>618</v>
+        <v>462</v>
       </c>
       <c r="H243" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I243" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B244" t="s">
         <v>29</v>
       </c>
       <c r="C244" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D244" t="s">
+        <v>1017</v>
+      </c>
+      <c r="E244" t="s">
         <v>1018</v>
       </c>
-      <c r="E244" t="s">
+      <c r="F244" t="s">
         <v>1019</v>
       </c>
-      <c r="F244" t="s">
-        <v>1020</v>
-      </c>
       <c r="G244">
-        <v>204</v>
+        <v>331</v>
       </c>
       <c r="H244" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I244" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B245" t="s">
         <v>29</v>
       </c>
       <c r="C245" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D245" t="s">
+        <v>1021</v>
+      </c>
+      <c r="E245" t="s">
         <v>1022</v>
       </c>
-      <c r="E245" t="s">
+      <c r="F245" t="s">
         <v>1023</v>
       </c>
-      <c r="F245" t="s">
-        <v>1024</v>
-      </c>
       <c r="G245">
-        <v>468</v>
+        <v>645</v>
       </c>
       <c r="H245" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I245" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="B246" t="s">
         <v>29</v>
       </c>
       <c r="C246" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D246" t="s">
+        <v>1025</v>
+      </c>
+      <c r="E246" t="s">
         <v>1026</v>
       </c>
-      <c r="E246" t="s">
+      <c r="F246" t="s">
         <v>1027</v>
       </c>
-      <c r="F246" t="s">
-        <v>1028</v>
-      </c>
       <c r="G246">
-        <v>279</v>
+        <v>373</v>
       </c>
       <c r="H246" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I246" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B247" t="s">
         <v>29</v>
       </c>
       <c r="C247" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D247" t="s">
+        <v>1029</v>
+      </c>
+      <c r="E247" t="s">
         <v>1030</v>
       </c>
-      <c r="E247" t="s">
+      <c r="F247" t="s">
         <v>1031</v>
       </c>
-      <c r="F247" t="s">
-        <v>1032</v>
-      </c>
       <c r="G247">
-        <v>249</v>
+        <v>268</v>
       </c>
       <c r="H247" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I247" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="B248" t="s">
         <v>29</v>
       </c>
       <c r="C248" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D248" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E248" t="s">
         <v>1034</v>
       </c>
-      <c r="E248" t="s">
+      <c r="F248" t="s">
         <v>1035</v>
       </c>
-      <c r="F248" t="s">
-        <v>1036</v>
-      </c>
       <c r="G248">
-        <v>373</v>
+        <v>518</v>
       </c>
       <c r="H248" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I248" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="B249" t="s">
         <v>29</v>
       </c>
       <c r="C249" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D249" t="s">
+        <v>1037</v>
+      </c>
+      <c r="E249" t="s">
         <v>1038</v>
       </c>
-      <c r="E249" t="s">
+      <c r="F249" t="s">
         <v>1039</v>
       </c>
-      <c r="F249" t="s">
-        <v>1040</v>
-      </c>
       <c r="G249">
-        <v>395</v>
+        <v>604</v>
       </c>
       <c r="H249" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I249" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="B250" t="s">
         <v>29</v>
       </c>
       <c r="C250" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D250" t="s">
+        <v>1041</v>
+      </c>
+      <c r="E250" t="s">
         <v>1042</v>
       </c>
-      <c r="E250" t="s">
+      <c r="F250" t="s">
         <v>1043</v>
       </c>
-      <c r="F250" t="s">
-        <v>1044</v>
-      </c>
       <c r="G250">
-        <v>373</v>
+        <v>329</v>
       </c>
       <c r="H250" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I250" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="251" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="B251" t="s">
         <v>29</v>
       </c>
       <c r="C251" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D251" t="s">
+        <v>1045</v>
+      </c>
+      <c r="E251" t="s">
         <v>1046</v>
       </c>
-      <c r="E251" t="s">
+      <c r="F251" t="s">
         <v>1047</v>
       </c>
-      <c r="F251" t="s">
-        <v>1048</v>
-      </c>
       <c r="G251">
-        <v>322</v>
+        <v>408</v>
       </c>
       <c r="H251" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I251" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="252" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="B252" t="s">
         <v>29</v>
       </c>
       <c r="C252" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D252" t="s">
+        <v>1049</v>
+      </c>
+      <c r="E252" t="s">
         <v>1050</v>
       </c>
-      <c r="E252" t="s">
+      <c r="F252" t="s">
         <v>1051</v>
       </c>
-      <c r="F252" t="s">
-        <v>1052</v>
-      </c>
       <c r="G252">
-        <v>588</v>
+        <v>404</v>
       </c>
       <c r="H252" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I252" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="253" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="B253" t="s">
         <v>29</v>
       </c>
       <c r="C253" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D253" t="s">
+        <v>1053</v>
+      </c>
+      <c r="E253" t="s">
         <v>1054</v>
       </c>
-      <c r="E253" t="s">
+      <c r="F253" t="s">
         <v>1055</v>
       </c>
-      <c r="F253" t="s">
-        <v>1056</v>
-      </c>
       <c r="G253">
-        <v>518</v>
+        <v>623</v>
       </c>
       <c r="H253" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I253" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="254" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="B254" t="s">
         <v>29</v>
       </c>
       <c r="C254" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D254" t="s">
+        <v>1057</v>
+      </c>
+      <c r="E254" t="s">
         <v>1058</v>
       </c>
-      <c r="E254" t="s">
+      <c r="F254" t="s">
         <v>1059</v>
       </c>
-      <c r="F254" t="s">
-        <v>1060</v>
-      </c>
       <c r="G254">
-        <v>606</v>
+        <v>618</v>
       </c>
       <c r="H254" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I254" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="255" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="B255" t="s">
         <v>29</v>
       </c>
       <c r="C255" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D255" t="s">
+        <v>1061</v>
+      </c>
+      <c r="E255" t="s">
         <v>1062</v>
       </c>
-      <c r="E255" t="s">
+      <c r="F255" t="s">
         <v>1063</v>
       </c>
-      <c r="F255" t="s">
-        <v>1064</v>
-      </c>
       <c r="G255">
-        <v>468</v>
+        <v>435</v>
       </c>
       <c r="H255" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I255" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="256" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="B256" t="s">
         <v>29</v>
       </c>
       <c r="C256" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D256" t="s">
+        <v>1065</v>
+      </c>
+      <c r="E256" t="s">
         <v>1066</v>
       </c>
-      <c r="E256" t="s">
+      <c r="F256" t="s">
         <v>1067</v>
       </c>
-      <c r="F256" t="s">
-        <v>1068</v>
-      </c>
       <c r="G256">
-        <v>466</v>
+        <v>572</v>
       </c>
       <c r="H256" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I256" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="257" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="B257" t="s">
         <v>29</v>
       </c>
       <c r="C257" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D257" t="s">
+        <v>1069</v>
+      </c>
+      <c r="E257" t="s">
         <v>1070</v>
       </c>
-      <c r="E257" t="s">
+      <c r="F257" t="s">
         <v>1071</v>
       </c>
-      <c r="F257" t="s">
-        <v>1072</v>
-      </c>
       <c r="G257">
-        <v>432</v>
+        <v>390</v>
       </c>
       <c r="H257" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I257" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="258" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="B258" t="s">
         <v>29</v>
       </c>
       <c r="C258" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D258" t="s">
+        <v>1073</v>
+      </c>
+      <c r="E258" t="s">
         <v>1074</v>
       </c>
-      <c r="E258" t="s">
+      <c r="F258" t="s">
         <v>1075</v>
       </c>
-      <c r="F258" t="s">
-        <v>1076</v>
-      </c>
       <c r="G258">
-        <v>563</v>
+        <v>621</v>
       </c>
       <c r="H258" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I258" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="259" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="B259" t="s">
         <v>29</v>
       </c>
       <c r="C259" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D259" t="s">
+        <v>1077</v>
+      </c>
+      <c r="E259" t="s">
         <v>1078</v>
       </c>
-      <c r="E259" t="s">
+      <c r="F259" t="s">
         <v>1079</v>
       </c>
-      <c r="F259" t="s">
-        <v>1080</v>
-      </c>
       <c r="G259">
-        <v>497</v>
+        <v>409</v>
       </c>
       <c r="H259" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I259" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="B260" t="s">
         <v>29</v>
       </c>
       <c r="C260" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D260" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E260" t="s">
         <v>1082</v>
       </c>
-      <c r="E260" t="s">
+      <c r="F260" t="s">
         <v>1083</v>
       </c>
-      <c r="F260" t="s">
-        <v>1084</v>
-      </c>
       <c r="G260">
-        <v>258</v>
+        <v>280</v>
       </c>
       <c r="H260" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I260" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="261" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="B261" t="s">
         <v>29</v>
       </c>
       <c r="C261" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D261" t="s">
+        <v>1085</v>
+      </c>
+      <c r="E261" t="s">
         <v>1086</v>
       </c>
-      <c r="E261" t="s">
+      <c r="F261" t="s">
         <v>1087</v>
       </c>
-      <c r="F261" t="s">
-        <v>1088</v>
-      </c>
       <c r="G261">
-        <v>361</v>
+        <v>258</v>
       </c>
       <c r="H261" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I261" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="262" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="B262" t="s">
         <v>29</v>
       </c>
       <c r="C262" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D262" t="s">
+        <v>1089</v>
+      </c>
+      <c r="E262" t="s">
         <v>1090</v>
       </c>
-      <c r="E262" t="s">
+      <c r="F262" t="s">
         <v>1091</v>
       </c>
-      <c r="F262" t="s">
-        <v>1092</v>
-      </c>
       <c r="G262">
-        <v>555</v>
+        <v>465</v>
       </c>
       <c r="H262" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I262" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="263" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="B263" t="s">
         <v>29</v>
       </c>
       <c r="C263" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D263" t="s">
+        <v>1093</v>
+      </c>
+      <c r="E263" t="s">
         <v>1094</v>
       </c>
-      <c r="E263" t="s">
+      <c r="F263" t="s">
         <v>1095</v>
       </c>
-      <c r="F263" t="s">
-        <v>1096</v>
-      </c>
       <c r="G263">
-        <v>616</v>
+        <v>215</v>
       </c>
       <c r="H263" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I263" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="264" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="B264" t="s">
         <v>29</v>
       </c>
       <c r="C264" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D264" t="s">
+        <v>1097</v>
+      </c>
+      <c r="E264" t="s">
         <v>1098</v>
       </c>
-      <c r="E264" t="s">
+      <c r="F264" t="s">
         <v>1099</v>
       </c>
-      <c r="F264" t="s">
-        <v>1100</v>
-      </c>
       <c r="G264">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H264" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I264" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="265" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="B265" t="s">
         <v>29</v>
       </c>
       <c r="C265" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D265" t="s">
+        <v>1101</v>
+      </c>
+      <c r="E265" t="s">
         <v>1102</v>
       </c>
-      <c r="E265" t="s">
+      <c r="F265" t="s">
         <v>1103</v>
       </c>
-      <c r="F265" t="s">
-        <v>1104</v>
-      </c>
       <c r="G265">
-        <v>271</v>
+        <v>301</v>
       </c>
       <c r="H265" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I265" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="266" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="B266" t="s">
         <v>29</v>
       </c>
       <c r="C266" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D266" t="s">
+        <v>1105</v>
+      </c>
+      <c r="E266" t="s">
         <v>1106</v>
       </c>
-      <c r="E266" t="s">
+      <c r="F266" t="s">
         <v>1107</v>
       </c>
-      <c r="F266" t="s">
-        <v>1108</v>
-      </c>
       <c r="G266">
-        <v>607</v>
+        <v>578</v>
       </c>
       <c r="H266" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I266" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="267" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="B267" t="s">
         <v>29</v>
       </c>
       <c r="C267" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D267" t="s">
+        <v>1109</v>
+      </c>
+      <c r="E267" t="s">
         <v>1110</v>
       </c>
-      <c r="E267" t="s">
+      <c r="F267" t="s">
         <v>1111</v>
       </c>
-      <c r="F267" t="s">
-        <v>1112</v>
-      </c>
       <c r="G267">
-        <v>473</v>
+        <v>533</v>
       </c>
       <c r="H267" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I267" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="268" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="B268" t="s">
         <v>29</v>
       </c>
       <c r="C268" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D268" t="s">
+        <v>1113</v>
+      </c>
+      <c r="E268" t="s">
         <v>1114</v>
       </c>
-      <c r="E268" t="s">
+      <c r="F268" t="s">
         <v>1115</v>
       </c>
-      <c r="F268" t="s">
-        <v>1116</v>
-      </c>
       <c r="G268">
-        <v>392</v>
+        <v>270</v>
       </c>
       <c r="H268" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I268" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="269" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="B269" t="s">
         <v>29</v>
       </c>
       <c r="C269" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D269" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E269" t="s">
         <v>1118</v>
       </c>
-      <c r="E269" t="s">
+      <c r="F269" t="s">
         <v>1119</v>
       </c>
-      <c r="F269" t="s">
-        <v>1120</v>
-      </c>
       <c r="G269">
-        <v>359</v>
+        <v>602</v>
       </c>
       <c r="H269" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I269" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="270" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="B270" t="s">
         <v>29</v>
       </c>
       <c r="C270" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D270" t="s">
+        <v>1121</v>
+      </c>
+      <c r="E270" t="s">
         <v>1122</v>
       </c>
-      <c r="E270" t="s">
+      <c r="F270" t="s">
         <v>1123</v>
       </c>
-      <c r="F270" t="s">
-        <v>1124</v>
-      </c>
       <c r="G270">
-        <v>337</v>
+        <v>358</v>
       </c>
       <c r="H270" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I270" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="271" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B271" t="s">
         <v>29</v>
       </c>
       <c r="C271" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="D271" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E271" t="s">
         <v>1126</v>
       </c>
-      <c r="E271" t="s">
+      <c r="F271" t="s">
         <v>1127</v>
       </c>
-      <c r="F271" t="s">
-        <v>1128</v>
-      </c>
       <c r="G271">
-        <v>436</v>
+        <v>576</v>
       </c>
       <c r="H271" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I271" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="272" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B272" t="s">
         <v>13</v>
       </c>
       <c r="C272" t="s">
+        <v>1129</v>
+      </c>
+      <c r="D272" t="s">
         <v>1130</v>
       </c>
-      <c r="D272" t="s">
+      <c r="E272" t="s">
         <v>1131</v>
       </c>
-      <c r="E272" t="s">
+      <c r="F272" t="s">
         <v>1132</v>
       </c>
-      <c r="F272" t="s">
-        <v>1133</v>
-      </c>
       <c r="G272">
-        <v>351</v>
+        <v>230</v>
       </c>
       <c r="H272" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I272" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="273" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="B273" t="s">
         <v>13</v>
       </c>
       <c r="C273" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="D273" t="s">
+        <v>1134</v>
+      </c>
+      <c r="E273" t="s">
         <v>1135</v>
       </c>
-      <c r="E273" t="s">
+      <c r="F273" t="s">
         <v>1136</v>
       </c>
-      <c r="F273" t="s">
-        <v>1137</v>
-      </c>
       <c r="G273">
-        <v>172</v>
+        <v>240</v>
       </c>
       <c r="H273" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I273" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="274" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="B274" t="s">
         <v>13</v>
       </c>
       <c r="C274" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="D274" t="s">
+        <v>1138</v>
+      </c>
+      <c r="E274" t="s">
         <v>1139</v>
       </c>
-      <c r="E274" t="s">
+      <c r="F274" t="s">
         <v>1140</v>
       </c>
-      <c r="F274" t="s">
-        <v>1141</v>
-      </c>
       <c r="G274">
-        <v>113</v>
+        <v>346</v>
       </c>
       <c r="H274" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I274" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="275" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="B275" t="s">
         <v>13</v>
       </c>
       <c r="C275" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="D275" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E275" t="s">
         <v>1143</v>
       </c>
-      <c r="E275" t="s">
+      <c r="F275" t="s">
         <v>1144</v>
       </c>
-      <c r="F275" t="s">
-        <v>1145</v>
-      </c>
       <c r="G275">
-        <v>191</v>
+        <v>159</v>
       </c>
       <c r="H275" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I275" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="276" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="B276" t="s">
         <v>13</v>
       </c>
       <c r="C276" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="D276" t="s">
+        <v>1146</v>
+      </c>
+      <c r="E276" t="s">
         <v>1147</v>
       </c>
-      <c r="E276" t="s">
+      <c r="F276" t="s">
         <v>1148</v>
       </c>
-      <c r="F276" t="s">
-        <v>1149</v>
-      </c>
       <c r="G276">
-        <v>316</v>
+        <v>361</v>
       </c>
       <c r="H276" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I276" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="277" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="B277" t="s">
         <v>13</v>
       </c>
       <c r="C277" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="D277" t="s">
+        <v>1150</v>
+      </c>
+      <c r="E277" t="s">
         <v>1151</v>
       </c>
-      <c r="E277" t="s">
+      <c r="F277" t="s">
         <v>1152</v>
       </c>
-      <c r="F277" t="s">
-        <v>1153</v>
-      </c>
       <c r="G277">
-        <v>348</v>
+        <v>300</v>
       </c>
       <c r="H277" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I277" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="278" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="B278" t="s">
         <v>13</v>
       </c>
       <c r="C278" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="D278" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E278" t="s">
         <v>1155</v>
       </c>
-      <c r="E278" t="s">
+      <c r="F278" t="s">
         <v>1156</v>
       </c>
-      <c r="F278" t="s">
-        <v>1157</v>
-      </c>
       <c r="G278">
-        <v>380</v>
+        <v>133</v>
       </c>
       <c r="H278" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I278" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="279" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="B279" t="s">
         <v>13</v>
       </c>
       <c r="C279" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="D279" t="s">
+        <v>1158</v>
+      </c>
+      <c r="E279" t="s">
         <v>1159</v>
       </c>
-      <c r="E279" t="s">
+      <c r="F279" t="s">
         <v>1160</v>
       </c>
-      <c r="F279" t="s">
-        <v>1161</v>
-      </c>
       <c r="G279">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="H279" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I279" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="280" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="B280" t="s">
         <v>13</v>
       </c>
       <c r="C280" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="D280" t="s">
+        <v>1162</v>
+      </c>
+      <c r="E280" t="s">
         <v>1163</v>
       </c>
-      <c r="E280" t="s">
+      <c r="F280" t="s">
         <v>1164</v>
       </c>
-      <c r="F280" t="s">
-        <v>1165</v>
-      </c>
       <c r="G280">
-        <v>322</v>
+        <v>386</v>
       </c>
       <c r="H280" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I280" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="B281" t="s">
         <v>13</v>
       </c>
       <c r="C281" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="D281" t="s">
+        <v>1166</v>
+      </c>
+      <c r="E281" t="s">
         <v>1167</v>
       </c>
-      <c r="E281" t="s">
+      <c r="F281" t="s">
         <v>1168</v>
       </c>
-      <c r="F281" t="s">
-        <v>1169</v>
-      </c>
       <c r="G281">
-        <v>236</v>
+        <v>263</v>
       </c>
       <c r="H281" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I281" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="282" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="B282" t="s">
         <v>13</v>
       </c>
       <c r="C282" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="D282" t="s">
+        <v>1170</v>
+      </c>
+      <c r="E282" t="s">
         <v>1171</v>
       </c>
-      <c r="E282" t="s">
+      <c r="F282" t="s">
         <v>1172</v>
       </c>
-      <c r="F282" t="s">
-        <v>1173</v>
-      </c>
       <c r="G282">
-        <v>319</v>
+        <v>201</v>
       </c>
       <c r="H282" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I282" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="283" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="B283" t="s">
         <v>13</v>
       </c>
       <c r="C283" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="D283" t="s">
+        <v>1174</v>
+      </c>
+      <c r="E283" t="s">
         <v>1175</v>
       </c>
-      <c r="E283" t="s">
+      <c r="F283" t="s">
         <v>1176</v>
       </c>
-      <c r="F283" t="s">
-        <v>1177</v>
-      </c>
       <c r="G283">
-        <v>390</v>
+        <v>290</v>
       </c>
       <c r="H283" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I283" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B284" t="s">
         <v>13</v>
       </c>
       <c r="C284" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="D284" t="s">
+        <v>1178</v>
+      </c>
+      <c r="E284" t="s">
         <v>1179</v>
       </c>
-      <c r="E284" t="s">
+      <c r="F284" t="s">
         <v>1180</v>
       </c>
-      <c r="F284" t="s">
-        <v>1181</v>
-      </c>
       <c r="G284">
-        <v>304</v>
+        <v>227</v>
       </c>
       <c r="H284" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I284" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="285" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="B285" t="s">
         <v>13</v>
       </c>
       <c r="C285" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="D285" t="s">
+        <v>1182</v>
+      </c>
+      <c r="E285" t="s">
         <v>1183</v>
       </c>
-      <c r="E285" t="s">
+      <c r="F285" t="s">
         <v>1184</v>
       </c>
-      <c r="F285" t="s">
-        <v>1185</v>
-      </c>
       <c r="G285">
-        <v>221</v>
+        <v>166</v>
       </c>
       <c r="H285" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I285" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="286" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="B286" t="s">
         <v>13</v>
       </c>
       <c r="C286" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="D286" t="s">
+        <v>1186</v>
+      </c>
+      <c r="E286" t="s">
         <v>1187</v>
       </c>
-      <c r="E286" t="s">
+      <c r="F286" t="s">
         <v>1188</v>
       </c>
-      <c r="F286" t="s">
-        <v>1189</v>
-      </c>
       <c r="G286">
-        <v>351</v>
+        <v>289</v>
       </c>
       <c r="H286" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I286" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="287" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="B287" t="s">
         <v>13</v>
       </c>
       <c r="C287" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="D287" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E287" t="s">
         <v>1191</v>
       </c>
-      <c r="E287" t="s">
+      <c r="F287" t="s">
         <v>1192</v>
       </c>
-      <c r="F287" t="s">
-        <v>1193</v>
-      </c>
       <c r="G287">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H287" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I287" t="s">
-        <v>290</v>
+        <v>52</v>
       </c>
     </row>
     <row r="288" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="B288" t="s">
         <v>13</v>
       </c>
       <c r="C288" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="D288" t="s">
+        <v>1194</v>
+      </c>
+      <c r="E288" t="s">
         <v>1195</v>
       </c>
-      <c r="E288" t="s">
+      <c r="F288" t="s">
         <v>1196</v>
       </c>
-      <c r="F288" t="s">
+      <c r="G288">
+        <v>155</v>
+      </c>
+      <c r="H288" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="I288" t="s">
         <v>1197</v>
-      </c>
-      <c r="G288">
-        <v>393</v>
-      </c>
-      <c r="H288" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="I288" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="289" spans="1:9" x14ac:dyDescent="0.25">
@@ -12818,7 +12818,7 @@
         <v>13</v>
       </c>
       <c r="C289" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="D289" t="s">
         <v>1199</v>
@@ -12830,13 +12830,13 @@
         <v>1201</v>
       </c>
       <c r="G289">
-        <v>353</v>
+        <v>196</v>
       </c>
       <c r="H289" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I289" t="s">
-        <v>290</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="290" spans="1:9" x14ac:dyDescent="0.25">
@@ -12847,7 +12847,7 @@
         <v>13</v>
       </c>
       <c r="C290" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="D290" t="s">
         <v>1203</v>
@@ -12859,13 +12859,13 @@
         <v>1205</v>
       </c>
       <c r="G290">
-        <v>393</v>
+        <v>197</v>
       </c>
       <c r="H290" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I290" t="s">
-        <v>290</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="291" spans="1:9" x14ac:dyDescent="0.25">
@@ -12876,7 +12876,7 @@
         <v>13</v>
       </c>
       <c r="C291" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="D291" t="s">
         <v>1207</v>
@@ -12888,13 +12888,13 @@
         <v>1209</v>
       </c>
       <c r="G291">
-        <v>225</v>
+        <v>394</v>
       </c>
       <c r="H291" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I291" t="s">
-        <v>290</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="292" spans="1:9" x14ac:dyDescent="0.25">
@@ -12905,7 +12905,7 @@
         <v>13</v>
       </c>
       <c r="C292" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="D292" t="s">
         <v>1211</v>
@@ -12917,13 +12917,13 @@
         <v>1213</v>
       </c>
       <c r="G292">
-        <v>372</v>
+        <v>290</v>
       </c>
       <c r="H292" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I292" t="s">
-        <v>290</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="293" spans="1:9" x14ac:dyDescent="0.25">
@@ -12934,7 +12934,7 @@
         <v>13</v>
       </c>
       <c r="C293" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="D293" t="s">
         <v>1215</v>
@@ -12946,13 +12946,13 @@
         <v>1217</v>
       </c>
       <c r="G293">
-        <v>254</v>
+        <v>112</v>
       </c>
       <c r="H293" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I293" t="s">
-        <v>290</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.25">
@@ -12963,7 +12963,7 @@
         <v>13</v>
       </c>
       <c r="C294" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="D294" t="s">
         <v>1219</v>
@@ -12975,13 +12975,13 @@
         <v>1221</v>
       </c>
       <c r="G294">
-        <v>353</v>
+        <v>274</v>
       </c>
       <c r="H294" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I294" t="s">
-        <v>290</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="295" spans="1:9" x14ac:dyDescent="0.25">
@@ -12992,7 +12992,7 @@
         <v>13</v>
       </c>
       <c r="C295" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="D295" t="s">
         <v>1223</v>
@@ -13004,13 +13004,13 @@
         <v>1225</v>
       </c>
       <c r="G295">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="H295" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I295" t="s">
-        <v>290</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="296" spans="1:9" x14ac:dyDescent="0.25">
@@ -13021,7 +13021,7 @@
         <v>13</v>
       </c>
       <c r="C296" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="D296" t="s">
         <v>1227</v>
@@ -13033,13 +13033,13 @@
         <v>1229</v>
       </c>
       <c r="G296">
-        <v>108</v>
+        <v>152</v>
       </c>
       <c r="H296" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I296" t="s">
-        <v>290</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="297" spans="1:9" x14ac:dyDescent="0.25">
@@ -13050,7 +13050,7 @@
         <v>13</v>
       </c>
       <c r="C297" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="D297" t="s">
         <v>1231</v>
@@ -13062,13 +13062,13 @@
         <v>1233</v>
       </c>
       <c r="G297">
-        <v>317</v>
+        <v>257</v>
       </c>
       <c r="H297" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I297" t="s">
-        <v>290</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="298" spans="1:9" x14ac:dyDescent="0.25">
@@ -13079,7 +13079,7 @@
         <v>13</v>
       </c>
       <c r="C298" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="D298" t="s">
         <v>1235</v>
@@ -13091,13 +13091,13 @@
         <v>1237</v>
       </c>
       <c r="G298">
-        <v>312</v>
+        <v>177</v>
       </c>
       <c r="H298" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I298" t="s">
-        <v>290</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="299" spans="1:9" x14ac:dyDescent="0.25">
@@ -13108,7 +13108,7 @@
         <v>13</v>
       </c>
       <c r="C299" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="D299" t="s">
         <v>1239</v>
@@ -13120,13 +13120,13 @@
         <v>1241</v>
       </c>
       <c r="G299">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="H299" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I299" t="s">
-        <v>290</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="300" spans="1:9" x14ac:dyDescent="0.25">
@@ -13137,7 +13137,7 @@
         <v>13</v>
       </c>
       <c r="C300" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="D300" t="s">
         <v>1243</v>
@@ -13149,13 +13149,13 @@
         <v>1245</v>
       </c>
       <c r="G300">
-        <v>153</v>
+        <v>373</v>
       </c>
       <c r="H300" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I300" t="s">
-        <v>290</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="301" spans="1:9" x14ac:dyDescent="0.25">
@@ -13166,7 +13166,7 @@
         <v>13</v>
       </c>
       <c r="C301" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="D301" t="s">
         <v>1247</v>
@@ -13178,13 +13178,13 @@
         <v>1249</v>
       </c>
       <c r="G301">
-        <v>179</v>
+        <v>334</v>
       </c>
       <c r="H301" s="10" t="s">
         <v>46</v>
       </c>
       <c r="I301" t="s">
-        <v>290</v>
+        <v>1197</v>
       </c>
     </row>
   </sheetData>
